--- a/raw data/HMBD_InputData_Metadata_06.10.2022/HMBD_InputData_Metadata_06.10.2022/FRA_InputData_Metadata_18.10.2021.xlsx
+++ b/raw data/HMBD_InputData_Metadata_06.10.2022/HMBD_InputData_Metadata_06.10.2022/FRA_InputData_Metadata_18.10.2021.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PROJET JUMEAUX INED-MNHM\DATABASE\RAW DATA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ontariogov-my.sharepoint.com/personal/thiemi_doi_ontario_ca/Documents/Documents/GitHub/TwinToTwin/raw data/HMBD_InputData_Metadata_06.10.2022/HMBD_InputData_Metadata_06.10.2022/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_E5DC92B5E18F4B927B9BDCFD84F9056F7E0ED4FF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCBE1982-4A80-4F3D-9D59-EEDC726AB02D}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="19416" windowHeight="10416" activeTab="3"/>
+    <workbookView xWindow="-110" yWindow="970" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="contents" sheetId="3" r:id="rId1"/>
@@ -20,7 +21,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'input data'!$A$1:$D$1</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,6 +29,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -1059,7 +1063,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="37" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
@@ -1575,42 +1579,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+  <cellXfs count="78">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="22" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1620,20 +1623,20 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1647,7 +1650,6 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1666,45 +1668,72 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1718,48 +1747,12 @@
     <xf numFmtId="0" fontId="23" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1792,7 +1785,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1"/>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1841,7 +1840,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1"/>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0200-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -1890,7 +1895,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Image 1"/>
+        <xdr:cNvPr id="2" name="Image 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0300-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -2119,100 +2130,100 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A8:K26"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="11.5546875" style="13"/>
+    <col min="1" max="16384" width="11.54296875" style="12"/>
   </cols>
   <sheetData>
-    <row r="8" spans="1:4" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
+    <row r="8" spans="1:4" ht="18" x14ac:dyDescent="0.4">
+      <c r="A8" s="11" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A9" s="51" t="s">
+    <row r="9" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="A9" s="46" t="s">
         <v>210</v>
       </c>
-      <c r="D9" s="52" t="s">
+      <c r="D9" s="47" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-    </row>
-    <row r="14" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+    <row r="13" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="A13" s="1"/>
+    </row>
+    <row r="14" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="A14" s="14" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A16" s="11"/>
-    </row>
-    <row r="17" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+    <row r="16" spans="1:4" ht="14" x14ac:dyDescent="0.3">
+      <c r="A16" s="1"/>
+    </row>
+    <row r="17" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A18" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A19" s="11"/>
-    </row>
-    <row r="20" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+    <row r="19" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A19" s="1"/>
+    </row>
+    <row r="20" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A20" s="14" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="11" t="s">
+    <row r="21" spans="1:11" ht="14" x14ac:dyDescent="0.3">
+      <c r="A21" s="1" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="15" x14ac:dyDescent="0.25">
-      <c r="A22" s="12"/>
+    <row r="22" spans="1:11" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A22" s="11"/>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="53" t="s">
+      <c r="A25" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="B25" s="54"/>
-      <c r="C25" s="55"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="55"/>
-      <c r="F25" s="55"/>
-      <c r="G25" s="55"/>
-      <c r="H25" s="55"/>
-      <c r="I25" s="55"/>
-      <c r="J25" s="55"/>
-      <c r="K25" s="55"/>
+      <c r="B25" s="49"/>
+      <c r="C25" s="50"/>
+      <c r="D25" s="50"/>
+      <c r="E25" s="50"/>
+      <c r="F25" s="50"/>
+      <c r="G25" s="50"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="50"/>
+      <c r="J25" s="50"/>
+      <c r="K25" s="50"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="51" t="s">
         <v>213</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A14" location="'input data'!A1" display="input data"/>
-    <hyperlink ref="A17" location="'metadata - variables input data'!A1" display="metadata - variables input data"/>
-    <hyperlink ref="A20" location="'metadata - sources &amp; notes'!A1" display="metadata - sources &amp; notes"/>
-    <hyperlink ref="D9" r:id="rId1"/>
-    <hyperlink ref="A26" r:id="rId2"/>
+    <hyperlink ref="A14" location="'input data'!A1" display="input data" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="A17" location="'metadata - variables input data'!A1" display="metadata - variables input data" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="A20" location="'metadata - sources &amp; notes'!A1" display="metadata - sources &amp; notes" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="D9" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="A26" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
@@ -2220,23 +2231,25 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AJ164"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11" style="8" customWidth="1"/>
-    <col min="3" max="3" width="7.44140625" style="8" customWidth="1"/>
+    <col min="3" max="3" width="7.453125" style="8" customWidth="1"/>
     <col min="4" max="4" width="11" style="8" customWidth="1"/>
-    <col min="5" max="18" width="14.44140625" style="7"/>
-    <col min="19" max="21" width="14.33203125" style="9" customWidth="1"/>
-    <col min="22" max="36" width="14.44140625" style="9"/>
-    <col min="37" max="16384" width="14.44140625" style="8"/>
+    <col min="5" max="8" width="14.453125" style="7"/>
+    <col min="9" max="9" width="14.36328125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="18" width="14.453125" style="7"/>
+    <col min="19" max="21" width="14.36328125" style="9" customWidth="1"/>
+    <col min="22" max="36" width="14.453125" style="9"/>
+    <col min="37" max="16384" width="14.453125" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" s="4" customFormat="1" ht="39.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" s="4" customFormat="1" ht="39.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2310,7 +2323,7 @@
       <c r="AI1" s="5"/>
       <c r="AJ1" s="5"/>
     </row>
-    <row r="2" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>125</v>
       </c>
@@ -2366,7 +2379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>125</v>
       </c>
@@ -2422,7 +2435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>125</v>
       </c>
@@ -2478,7 +2491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>125</v>
       </c>
@@ -2534,7 +2547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>125</v>
       </c>
@@ -2590,7 +2603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>125</v>
       </c>
@@ -2646,7 +2659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>125</v>
       </c>
@@ -2703,7 +2716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>125</v>
       </c>
@@ -2759,7 +2772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A10" s="6" t="s">
         <v>125</v>
       </c>
@@ -2815,7 +2828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A11" s="6" t="s">
         <v>125</v>
       </c>
@@ -2871,7 +2884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A12" s="6" t="s">
         <v>125</v>
       </c>
@@ -2927,7 +2940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A13" s="6" t="s">
         <v>125</v>
       </c>
@@ -2983,7 +2996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>125</v>
       </c>
@@ -3039,7 +3052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>125</v>
       </c>
@@ -3095,7 +3108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>125</v>
       </c>
@@ -3151,7 +3164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>125</v>
       </c>
@@ -3207,7 +3220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>125</v>
       </c>
@@ -3263,7 +3276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>125</v>
       </c>
@@ -3319,7 +3332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>125</v>
       </c>
@@ -3375,7 +3388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>125</v>
       </c>
@@ -3431,7 +3444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
         <v>125</v>
       </c>
@@ -3487,7 +3500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A23" s="6" t="s">
         <v>125</v>
       </c>
@@ -3543,7 +3556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A24" s="6" t="s">
         <v>125</v>
       </c>
@@ -3599,7 +3612,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A25" s="6" t="s">
         <v>125</v>
       </c>
@@ -3655,7 +3668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A26" s="6" t="s">
         <v>125</v>
       </c>
@@ -3711,7 +3724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A27" s="6" t="s">
         <v>125</v>
       </c>
@@ -3767,7 +3780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A28" s="6" t="s">
         <v>125</v>
       </c>
@@ -3823,7 +3836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A29" s="6" t="s">
         <v>125</v>
       </c>
@@ -3879,7 +3892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A30" s="6" t="s">
         <v>125</v>
       </c>
@@ -3935,7 +3948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A31" s="6" t="s">
         <v>125</v>
       </c>
@@ -3991,7 +4004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A32" s="6" t="s">
         <v>125</v>
       </c>
@@ -4047,7 +4060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A33" s="6" t="s">
         <v>125</v>
       </c>
@@ -4103,7 +4116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A34" s="6" t="s">
         <v>125</v>
       </c>
@@ -4159,7 +4172,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A35" s="6" t="s">
         <v>125</v>
       </c>
@@ -4215,7 +4228,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A36" s="6" t="s">
         <v>125</v>
       </c>
@@ -4271,7 +4284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A37" s="6" t="s">
         <v>125</v>
       </c>
@@ -4327,7 +4340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A38" s="6" t="s">
         <v>125</v>
       </c>
@@ -4383,7 +4396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A39" s="6" t="s">
         <v>125</v>
       </c>
@@ -4439,7 +4452,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A40" s="6" t="s">
         <v>125</v>
       </c>
@@ -4495,7 +4508,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A41" s="6" t="s">
         <v>125</v>
       </c>
@@ -4551,7 +4564,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A42" s="6" t="s">
         <v>125</v>
       </c>
@@ -4607,7 +4620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A43" s="6" t="s">
         <v>125</v>
       </c>
@@ -4663,7 +4676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A44" s="6" t="s">
         <v>125</v>
       </c>
@@ -4719,7 +4732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A45" s="6" t="s">
         <v>125</v>
       </c>
@@ -4775,7 +4788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A46" s="6" t="s">
         <v>125</v>
       </c>
@@ -4831,7 +4844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A47" s="6" t="s">
         <v>125</v>
       </c>
@@ -4887,7 +4900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A48" s="6" t="s">
         <v>125</v>
       </c>
@@ -4943,7 +4956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A49" s="6" t="s">
         <v>125</v>
       </c>
@@ -4999,7 +5012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A50" s="6" t="s">
         <v>125</v>
       </c>
@@ -5055,7 +5068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A51" s="6" t="s">
         <v>125</v>
       </c>
@@ -5111,7 +5124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A52" s="6" t="s">
         <v>125</v>
       </c>
@@ -5167,7 +5180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A53" s="6" t="s">
         <v>125</v>
       </c>
@@ -5223,7 +5236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A54" s="6" t="s">
         <v>125</v>
       </c>
@@ -5279,7 +5292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A55" s="6" t="s">
         <v>125</v>
       </c>
@@ -5335,7 +5348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A56" s="6" t="s">
         <v>125</v>
       </c>
@@ -5391,7 +5404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A57" s="6" t="s">
         <v>125</v>
       </c>
@@ -5447,7 +5460,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A58" s="6" t="s">
         <v>125</v>
       </c>
@@ -5503,7 +5516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A59" s="6" t="s">
         <v>125</v>
       </c>
@@ -5559,7 +5572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A60" s="6" t="s">
         <v>125</v>
       </c>
@@ -5615,7 +5628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A61" s="6" t="s">
         <v>125</v>
       </c>
@@ -5671,7 +5684,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A62" s="6" t="s">
         <v>125</v>
       </c>
@@ -5727,7 +5740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A63" s="6" t="s">
         <v>125</v>
       </c>
@@ -5783,7 +5796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A64" s="6" t="s">
         <v>125</v>
       </c>
@@ -5839,7 +5852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A65" s="6" t="s">
         <v>125</v>
       </c>
@@ -5895,7 +5908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A66" s="6" t="s">
         <v>125</v>
       </c>
@@ -5951,7 +5964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A67" s="6" t="s">
         <v>125</v>
       </c>
@@ -6007,7 +6020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A68" s="6" t="s">
         <v>125</v>
       </c>
@@ -6063,7 +6076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A69" s="6" t="s">
         <v>125</v>
       </c>
@@ -6119,7 +6132,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A70" s="6" t="s">
         <v>125</v>
       </c>
@@ -6175,7 +6188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A71" s="6" t="s">
         <v>125</v>
       </c>
@@ -6231,7 +6244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A72" s="6" t="s">
         <v>125</v>
       </c>
@@ -6287,7 +6300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A73" s="6" t="s">
         <v>125</v>
       </c>
@@ -6343,7 +6356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A74" s="6" t="s">
         <v>125</v>
       </c>
@@ -6399,7 +6412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A75" s="6" t="s">
         <v>125</v>
       </c>
@@ -6455,7 +6468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A76" s="6" t="s">
         <v>125</v>
       </c>
@@ -6511,7 +6524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A77" s="6" t="s">
         <v>125</v>
       </c>
@@ -6567,7 +6580,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A78" s="6" t="s">
         <v>125</v>
       </c>
@@ -6623,7 +6636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A79" s="6" t="s">
         <v>125</v>
       </c>
@@ -6679,7 +6692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A80" s="6" t="s">
         <v>125</v>
       </c>
@@ -6735,7 +6748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A81" s="6" t="s">
         <v>125</v>
       </c>
@@ -6791,7 +6804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A82" s="6" t="s">
         <v>125</v>
       </c>
@@ -6847,7 +6860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A83" s="6" t="s">
         <v>125</v>
       </c>
@@ -6903,7 +6916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A84" s="6" t="s">
         <v>125</v>
       </c>
@@ -6959,7 +6972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A85" s="6" t="s">
         <v>125</v>
       </c>
@@ -7015,7 +7028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A86" s="6" t="s">
         <v>125</v>
       </c>
@@ -7071,7 +7084,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A87" s="6" t="s">
         <v>125</v>
       </c>
@@ -7127,7 +7140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A88" s="6" t="s">
         <v>125</v>
       </c>
@@ -7183,7 +7196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A89" s="6" t="s">
         <v>125</v>
       </c>
@@ -7239,7 +7252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A90" s="6" t="s">
         <v>125</v>
       </c>
@@ -7295,7 +7308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A91" s="6" t="s">
         <v>125</v>
       </c>
@@ -7351,7 +7364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A92" s="6" t="s">
         <v>125</v>
       </c>
@@ -7407,7 +7420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A93" s="6" t="s">
         <v>125</v>
       </c>
@@ -7463,7 +7476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A94" s="6" t="s">
         <v>125</v>
       </c>
@@ -7519,7 +7532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A95" s="6" t="s">
         <v>125</v>
       </c>
@@ -7575,7 +7588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A96" s="6" t="s">
         <v>125</v>
       </c>
@@ -7631,7 +7644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A97" s="6" t="s">
         <v>125</v>
       </c>
@@ -7687,7 +7700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A98" s="6" t="s">
         <v>125</v>
       </c>
@@ -7743,7 +7756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A99" s="6" t="s">
         <v>125</v>
       </c>
@@ -7799,7 +7812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A100" s="6" t="s">
         <v>125</v>
       </c>
@@ -7855,7 +7868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A101" s="6" t="s">
         <v>125</v>
       </c>
@@ -7911,7 +7924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A102" s="6" t="s">
         <v>125</v>
       </c>
@@ -7967,7 +7980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A103" s="6" t="s">
         <v>125</v>
       </c>
@@ -8023,7 +8036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A104" s="6" t="s">
         <v>125</v>
       </c>
@@ -8079,7 +8092,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A105" s="6" t="s">
         <v>125</v>
       </c>
@@ -8135,7 +8148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A106" s="6" t="s">
         <v>125</v>
       </c>
@@ -8191,7 +8204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A107" s="6" t="s">
         <v>125</v>
       </c>
@@ -8247,7 +8260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A108" s="6" t="s">
         <v>125</v>
       </c>
@@ -8303,7 +8316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A109" s="6" t="s">
         <v>125</v>
       </c>
@@ -8359,7 +8372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A110" s="6" t="s">
         <v>125</v>
       </c>
@@ -8415,7 +8428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A111" s="6" t="s">
         <v>125</v>
       </c>
@@ -8471,7 +8484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A112" s="6" t="s">
         <v>125</v>
       </c>
@@ -8527,7 +8540,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A113" s="6" t="s">
         <v>125</v>
       </c>
@@ -8583,7 +8596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A114" s="6" t="s">
         <v>125</v>
       </c>
@@ -8639,7 +8652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A115" s="6" t="s">
         <v>125</v>
       </c>
@@ -8695,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A116" s="6" t="s">
         <v>125</v>
       </c>
@@ -8751,7 +8764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A117" s="6" t="s">
         <v>125</v>
       </c>
@@ -8807,7 +8820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A118" s="6" t="s">
         <v>125</v>
       </c>
@@ -8863,7 +8876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A119" s="6" t="s">
         <v>125</v>
       </c>
@@ -8919,7 +8932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A120" s="6" t="s">
         <v>125</v>
       </c>
@@ -8975,7 +8988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A121" s="6" t="s">
         <v>125</v>
       </c>
@@ -9031,7 +9044,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A122" s="6" t="s">
         <v>125</v>
       </c>
@@ -9087,7 +9100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A123" s="6" t="s">
         <v>125</v>
       </c>
@@ -9143,7 +9156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A124" s="6" t="s">
         <v>125</v>
       </c>
@@ -9199,7 +9212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A125" s="6" t="s">
         <v>125</v>
       </c>
@@ -9255,7 +9268,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A126" s="6" t="s">
         <v>125</v>
       </c>
@@ -9311,7 +9324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A127" s="6" t="s">
         <v>125</v>
       </c>
@@ -9367,7 +9380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A128" s="6" t="s">
         <v>125</v>
       </c>
@@ -9423,7 +9436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A129" s="6" t="s">
         <v>125</v>
       </c>
@@ -9479,7 +9492,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A130" s="6" t="s">
         <v>125</v>
       </c>
@@ -9535,7 +9548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A131" s="6" t="s">
         <v>125</v>
       </c>
@@ -9591,7 +9604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A132" s="6" t="s">
         <v>125</v>
       </c>
@@ -9647,7 +9660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A133" s="6" t="s">
         <v>125</v>
       </c>
@@ -9703,7 +9716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A134" s="6" t="s">
         <v>125</v>
       </c>
@@ -9759,7 +9772,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A135" s="6" t="s">
         <v>125</v>
       </c>
@@ -9815,7 +9828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A136" s="6" t="s">
         <v>125</v>
       </c>
@@ -9871,7 +9884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A137" s="6" t="s">
         <v>125</v>
       </c>
@@ -9927,7 +9940,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A138" s="6" t="s">
         <v>125</v>
       </c>
@@ -9983,7 +9996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A139" s="6" t="s">
         <v>125</v>
       </c>
@@ -10039,7 +10052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A140" s="6" t="s">
         <v>125</v>
       </c>
@@ -10095,7 +10108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A141" s="6" t="s">
         <v>125</v>
       </c>
@@ -10151,7 +10164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A142" s="6" t="s">
         <v>125</v>
       </c>
@@ -10207,7 +10220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A143" s="6" t="s">
         <v>125</v>
       </c>
@@ -10263,7 +10276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A144" s="6" t="s">
         <v>125</v>
       </c>
@@ -10319,7 +10332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A145" s="6" t="s">
         <v>125</v>
       </c>
@@ -10375,7 +10388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A146" s="6" t="s">
         <v>125</v>
       </c>
@@ -10431,7 +10444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A147" s="6" t="s">
         <v>125</v>
       </c>
@@ -10487,7 +10500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A148" s="6" t="s">
         <v>125</v>
       </c>
@@ -10543,7 +10556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A149" s="6" t="s">
         <v>125</v>
       </c>
@@ -10599,7 +10612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A150" s="6" t="s">
         <v>125</v>
       </c>
@@ -10655,7 +10668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A151" s="6" t="s">
         <v>125</v>
       </c>
@@ -10711,7 +10724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A152" s="6" t="s">
         <v>125</v>
       </c>
@@ -10767,7 +10780,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A153" s="6" t="s">
         <v>125</v>
       </c>
@@ -10823,7 +10836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A154" s="6" t="s">
         <v>125</v>
       </c>
@@ -10879,7 +10892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A155" s="6" t="s">
         <v>125</v>
       </c>
@@ -10935,7 +10948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A156" s="6" t="s">
         <v>125</v>
       </c>
@@ -10991,7 +11004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A157" s="6" t="s">
         <v>125</v>
       </c>
@@ -11047,7 +11060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A158" s="6" t="s">
         <v>125</v>
       </c>
@@ -11103,7 +11116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A159" s="6" t="s">
         <v>125</v>
       </c>
@@ -11159,7 +11172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A160" s="6" t="s">
         <v>125</v>
       </c>
@@ -11215,7 +11228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A161" s="6" t="s">
         <v>125</v>
       </c>
@@ -11271,7 +11284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="12.5" x14ac:dyDescent="0.25">
       <c r="A162" s="6" t="s">
         <v>125</v>
       </c>
@@ -11328,10 +11341,10 @@
       </c>
     </row>
     <row r="163" spans="1:18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="47" t="s">
-        <v>125</v>
-      </c>
-      <c r="B163" s="47" t="s">
+      <c r="A163" s="45" t="s">
+        <v>125</v>
+      </c>
+      <c r="B163" s="45" t="s">
         <v>124</v>
       </c>
       <c r="C163" s="8">
@@ -11440,7 +11453,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState ref="A2:D170">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D170">
     <sortCondition ref="C2:C170"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11449,247 +11462,247 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11.54296875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.88671875" style="24" customWidth="1"/>
-    <col min="2" max="2" width="75.109375" style="13" customWidth="1"/>
-    <col min="3" max="16384" width="11.5546875" style="13"/>
+    <col min="1" max="1" width="29.90625" style="23" customWidth="1"/>
+    <col min="2" max="2" width="75.08984375" style="12" customWidth="1"/>
+    <col min="3" max="16384" width="11.54296875" style="12"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="13"/>
+      <c r="A1" s="12"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="13"/>
+      <c r="A2" s="12"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="13"/>
+      <c r="A3" s="12"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="13"/>
+      <c r="A4" s="12"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="13"/>
-      <c r="B5" s="57" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="52" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="13"/>
-    </row>
-    <row r="7" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A6" s="12"/>
+    </row>
+    <row r="7" spans="1:2" ht="15.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="15" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="16"/>
-    </row>
-    <row r="9" spans="1:2" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
+    <row r="8" spans="1:2" ht="16" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="15"/>
+    </row>
+    <row r="9" spans="1:2" ht="15.5" x14ac:dyDescent="0.25">
+      <c r="A9" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="17" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+    <row r="10" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A10" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="B11" s="20" t="s">
+    <row r="11" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="19" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+    <row r="12" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="53" t="s">
         <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="66" t="s">
+      <c r="A13" s="73" t="s">
         <v>126</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="53" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="66"/>
-      <c r="B14" s="59" t="s">
+      <c r="A14" s="73"/>
+      <c r="B14" s="54" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="66"/>
-      <c r="B15" s="59" t="s">
+      <c r="A15" s="73"/>
+      <c r="B15" s="54" t="s">
         <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="66"/>
-      <c r="B16" s="59" t="s">
+      <c r="A16" s="73"/>
+      <c r="B16" s="54" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="66"/>
-      <c r="B17" s="60" t="s">
+      <c r="A17" s="73"/>
+      <c r="B17" s="55" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
+    <row r="18" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A18" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="B18" s="60" t="s">
+      <c r="B18" s="55" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+    <row r="19" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A19" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="19" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+    <row r="20" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A20" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="B20" s="20" t="s">
+      <c r="B20" s="19" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
+    <row r="21" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A21" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="B21" s="20" t="s">
+      <c r="B21" s="19" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
+    <row r="22" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A22" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="19" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
+    <row r="23" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A23" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="19" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+    <row r="24" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A24" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="19" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+    <row r="25" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A25" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="19" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
+    <row r="26" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A26" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B26" s="22" t="s">
+      <c r="B26" s="21" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
+    <row r="27" spans="1:2" ht="13.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="19" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
+    <row r="28" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A28" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="B28" s="20" t="s">
+      <c r="B28" s="19" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
+    <row r="29" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A29" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="21" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+    <row r="30" spans="1:2" ht="13" x14ac:dyDescent="0.3">
+      <c r="A30" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="61" t="s">
+      <c r="B30" s="56" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="39.6" x14ac:dyDescent="0.25">
-      <c r="A31" s="67" t="s">
+    <row r="31" spans="1:2" ht="38" x14ac:dyDescent="0.25">
+      <c r="A31" s="74" t="s">
         <v>214</v>
       </c>
-      <c r="B31" s="62" t="s">
+      <c r="B31" s="57" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="68"/>
-      <c r="B32" s="59" t="s">
+      <c r="A32" s="75"/>
+      <c r="B32" s="54" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="69"/>
-      <c r="B33" s="63" t="s">
+    <row r="33" spans="1:2" ht="13" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="76"/>
+      <c r="B33" s="58" t="s">
         <v>217</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="70" t="s">
+      <c r="A34" s="77" t="s">
         <v>178</v>
       </c>
-      <c r="B34" s="70"/>
+      <c r="B34" s="77"/>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="70"/>
-      <c r="B35" s="70"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="77"/>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="23" t="s">
+      <c r="A36" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="B36" s="23"/>
+      <c r="B36" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -11698,7 +11711,7 @@
     <mergeCell ref="A34:B35"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId2"/>
@@ -11706,2585 +11719,2540 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A3:U117"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="16384" width="8.77734375" style="11"/>
+    <col min="1" max="16384" width="8.81640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="64"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="T5" s="65" t="s">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="59"/>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="T5" s="60" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="14.4" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="77" t="s">
+    <row r="6" spans="1:21" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="7" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="61" t="s">
         <v>139</v>
       </c>
-      <c r="B7" s="78"/>
-      <c r="C7" s="78"/>
-      <c r="D7" s="78"/>
-      <c r="E7" s="78"/>
-      <c r="F7" s="78"/>
-      <c r="G7" s="78"/>
-      <c r="H7" s="78"/>
-      <c r="I7" s="78"/>
-      <c r="J7" s="78"/>
-      <c r="K7" s="78"/>
-      <c r="L7" s="78"/>
-      <c r="M7" s="78"/>
-      <c r="N7" s="78"/>
-      <c r="O7" s="78"/>
-      <c r="P7" s="78"/>
-      <c r="Q7" s="78"/>
-      <c r="R7" s="78"/>
-      <c r="S7" s="78"/>
-      <c r="T7" s="78"/>
-      <c r="U7" s="79"/>
-    </row>
-    <row r="8" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="80"/>
-      <c r="B8" s="81"/>
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="81"/>
-      <c r="F8" s="81"/>
-      <c r="G8" s="81"/>
-      <c r="H8" s="81"/>
-      <c r="I8" s="81"/>
-      <c r="J8" s="81"/>
-      <c r="K8" s="81"/>
-      <c r="L8" s="81"/>
-      <c r="M8" s="81"/>
-      <c r="N8" s="81"/>
-      <c r="O8" s="81"/>
-      <c r="P8" s="81"/>
-      <c r="Q8" s="81"/>
-      <c r="R8" s="81"/>
-      <c r="S8" s="81"/>
-      <c r="T8" s="81"/>
-      <c r="U8" s="82"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="25" t="s">
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
+      <c r="F7" s="62"/>
+      <c r="G7" s="62"/>
+      <c r="H7" s="62"/>
+      <c r="I7" s="62"/>
+      <c r="J7" s="62"/>
+      <c r="K7" s="62"/>
+      <c r="L7" s="62"/>
+      <c r="M7" s="62"/>
+      <c r="N7" s="62"/>
+      <c r="O7" s="62"/>
+      <c r="P7" s="62"/>
+      <c r="Q7" s="62"/>
+      <c r="R7" s="62"/>
+      <c r="S7" s="62"/>
+      <c r="T7" s="62"/>
+      <c r="U7" s="63"/>
+    </row>
+    <row r="8" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="64"/>
+      <c r="B8" s="65"/>
+      <c r="C8" s="65"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="G8" s="65"/>
+      <c r="H8" s="65"/>
+      <c r="I8" s="65"/>
+      <c r="J8" s="65"/>
+      <c r="K8" s="65"/>
+      <c r="L8" s="65"/>
+      <c r="M8" s="65"/>
+      <c r="N8" s="65"/>
+      <c r="O8" s="65"/>
+      <c r="P8" s="65"/>
+      <c r="Q8" s="65"/>
+      <c r="R8" s="65"/>
+      <c r="S8" s="65"/>
+      <c r="T8" s="65"/>
+      <c r="U8" s="66"/>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="27"/>
-      <c r="E9" s="27"/>
-      <c r="F9" s="27"/>
-      <c r="G9" s="27"/>
-      <c r="H9" s="27"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="27"/>
-      <c r="K9" s="27"/>
-      <c r="L9" s="27"/>
-      <c r="M9" s="27"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="27"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
-      <c r="R9" s="27"/>
-      <c r="S9" s="27"/>
-      <c r="T9" s="27"/>
-      <c r="U9" s="28"/>
-    </row>
-    <row r="10" spans="1:21" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="71" t="s">
+      <c r="B9" s="25"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="26"/>
+      <c r="K9" s="26"/>
+      <c r="L9" s="26"/>
+      <c r="M9" s="26"/>
+      <c r="N9" s="26"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
+      <c r="R9" s="26"/>
+      <c r="S9" s="26"/>
+      <c r="T9" s="26"/>
+      <c r="U9" s="27"/>
+    </row>
+    <row r="10" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="70" t="s">
         <v>222</v>
       </c>
-      <c r="B10" s="72"/>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="72"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-      <c r="J10" s="72"/>
-      <c r="K10" s="72"/>
-      <c r="L10" s="72"/>
-      <c r="M10" s="72"/>
-      <c r="N10" s="72"/>
-      <c r="O10" s="72"/>
-      <c r="P10" s="72"/>
-      <c r="Q10" s="72"/>
-      <c r="R10" s="72"/>
-      <c r="S10" s="72"/>
-      <c r="T10" s="72"/>
-      <c r="U10" s="73"/>
-    </row>
-    <row r="11" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="72"/>
-      <c r="F11" s="72"/>
-      <c r="G11" s="72"/>
-      <c r="H11" s="72"/>
-      <c r="I11" s="72"/>
-      <c r="J11" s="72"/>
-      <c r="K11" s="72"/>
-      <c r="L11" s="72"/>
-      <c r="M11" s="72"/>
-      <c r="N11" s="72"/>
-      <c r="O11" s="72"/>
-      <c r="P11" s="72"/>
-      <c r="Q11" s="72"/>
-      <c r="R11" s="72"/>
-      <c r="S11" s="72"/>
-      <c r="T11" s="72"/>
-      <c r="U11" s="73"/>
-    </row>
-    <row r="12" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="71"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="72"/>
-      <c r="F12" s="72"/>
-      <c r="G12" s="72"/>
-      <c r="H12" s="72"/>
-      <c r="I12" s="72"/>
-      <c r="J12" s="72"/>
-      <c r="K12" s="72"/>
-      <c r="L12" s="72"/>
-      <c r="M12" s="72"/>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="72"/>
-      <c r="S12" s="72"/>
-      <c r="T12" s="72"/>
-      <c r="U12" s="73"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="29" t="s">
+      <c r="B10" s="71"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="71"/>
+      <c r="F10" s="71"/>
+      <c r="G10" s="71"/>
+      <c r="H10" s="71"/>
+      <c r="I10" s="71"/>
+      <c r="J10" s="71"/>
+      <c r="K10" s="71"/>
+      <c r="L10" s="71"/>
+      <c r="M10" s="71"/>
+      <c r="N10" s="71"/>
+      <c r="O10" s="71"/>
+      <c r="P10" s="71"/>
+      <c r="Q10" s="71"/>
+      <c r="R10" s="71"/>
+      <c r="S10" s="71"/>
+      <c r="T10" s="71"/>
+      <c r="U10" s="72"/>
+    </row>
+    <row r="11" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="70"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="71"/>
+      <c r="D11" s="71"/>
+      <c r="E11" s="71"/>
+      <c r="F11" s="71"/>
+      <c r="G11" s="71"/>
+      <c r="H11" s="71"/>
+      <c r="I11" s="71"/>
+      <c r="J11" s="71"/>
+      <c r="K11" s="71"/>
+      <c r="L11" s="71"/>
+      <c r="M11" s="71"/>
+      <c r="N11" s="71"/>
+      <c r="O11" s="71"/>
+      <c r="P11" s="71"/>
+      <c r="Q11" s="71"/>
+      <c r="R11" s="71"/>
+      <c r="S11" s="71"/>
+      <c r="T11" s="71"/>
+      <c r="U11" s="72"/>
+    </row>
+    <row r="12" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="70"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="71"/>
+      <c r="D12" s="71"/>
+      <c r="E12" s="71"/>
+      <c r="F12" s="71"/>
+      <c r="G12" s="71"/>
+      <c r="H12" s="71"/>
+      <c r="I12" s="71"/>
+      <c r="J12" s="71"/>
+      <c r="K12" s="71"/>
+      <c r="L12" s="71"/>
+      <c r="M12" s="71"/>
+      <c r="N12" s="71"/>
+      <c r="O12" s="71"/>
+      <c r="P12" s="71"/>
+      <c r="Q12" s="71"/>
+      <c r="R12" s="71"/>
+      <c r="S12" s="71"/>
+      <c r="T12" s="71"/>
+      <c r="U12" s="72"/>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="27"/>
-      <c r="L13" s="27"/>
-      <c r="M13" s="27"/>
-      <c r="N13" s="27"/>
-      <c r="O13" s="27"/>
-      <c r="P13" s="27"/>
-      <c r="Q13" s="27"/>
-      <c r="R13" s="27"/>
-      <c r="S13" s="27"/>
-      <c r="T13" s="27"/>
-      <c r="U13" s="28"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="26"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="26"/>
+      <c r="L13" s="26"/>
+      <c r="M13" s="26"/>
+      <c r="N13" s="26"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="26"/>
+      <c r="Q13" s="26"/>
+      <c r="R13" s="26"/>
+      <c r="S13" s="26"/>
+      <c r="T13" s="26"/>
+      <c r="U13" s="27"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="29" t="s">
         <v>141</v>
       </c>
-      <c r="B14" s="27"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="27"/>
-      <c r="E14" s="27"/>
-      <c r="F14" s="27"/>
-      <c r="G14" s="27"/>
-      <c r="H14" s="27"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="27"/>
-      <c r="K14" s="27"/>
-      <c r="L14" s="27"/>
-      <c r="M14" s="27"/>
-      <c r="N14" s="27"/>
-      <c r="O14" s="27"/>
-      <c r="P14" s="27"/>
-      <c r="Q14" s="27"/>
-      <c r="R14" s="27"/>
-      <c r="S14" s="27"/>
-      <c r="T14" s="27"/>
-      <c r="U14" s="28"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="30"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="27"/>
-      <c r="H15" s="27"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="27"/>
-      <c r="K15" s="27"/>
-      <c r="L15" s="27"/>
-      <c r="M15" s="27"/>
-      <c r="N15" s="27"/>
-      <c r="O15" s="27"/>
-      <c r="P15" s="27"/>
-      <c r="Q15" s="27"/>
-      <c r="R15" s="27"/>
-      <c r="S15" s="27"/>
-      <c r="T15" s="27"/>
-      <c r="U15" s="28"/>
-    </row>
-    <row r="16" spans="1:21" ht="14.55" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="71" t="s">
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="M14" s="26"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
+      <c r="R14" s="26"/>
+      <c r="S14" s="26"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="27"/>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15" s="29"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="26"/>
+      <c r="D15" s="26"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="26"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="26"/>
+      <c r="L15" s="26"/>
+      <c r="M15" s="26"/>
+      <c r="N15" s="26"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="26"/>
+      <c r="Q15" s="26"/>
+      <c r="R15" s="26"/>
+      <c r="S15" s="26"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="27"/>
+    </row>
+    <row r="16" spans="1:21" ht="14.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="70" t="s">
         <v>142</v>
       </c>
-      <c r="B16" s="72"/>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="72"/>
-      <c r="F16" s="72"/>
-      <c r="G16" s="72"/>
-      <c r="H16" s="72"/>
-      <c r="I16" s="72"/>
-      <c r="J16" s="72"/>
-      <c r="K16" s="72"/>
-      <c r="L16" s="72"/>
-      <c r="M16" s="72"/>
-      <c r="N16" s="72"/>
-      <c r="O16" s="72"/>
-      <c r="P16" s="72"/>
-      <c r="Q16" s="72"/>
-      <c r="R16" s="72"/>
-      <c r="S16" s="72"/>
-      <c r="T16" s="72"/>
-      <c r="U16" s="73"/>
-    </row>
-    <row r="17" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="71"/>
-      <c r="B17" s="72"/>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72"/>
-      <c r="F17" s="72"/>
-      <c r="G17" s="72"/>
-      <c r="H17" s="72"/>
-      <c r="I17" s="72"/>
-      <c r="J17" s="72"/>
-      <c r="K17" s="72"/>
-      <c r="L17" s="72"/>
-      <c r="M17" s="72"/>
-      <c r="N17" s="72"/>
-      <c r="O17" s="72"/>
-      <c r="P17" s="72"/>
-      <c r="Q17" s="72"/>
-      <c r="R17" s="72"/>
-      <c r="S17" s="72"/>
-      <c r="T17" s="72"/>
-      <c r="U17" s="73"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="31" t="s">
+      <c r="B16" s="71"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="71"/>
+      <c r="F16" s="71"/>
+      <c r="G16" s="71"/>
+      <c r="H16" s="71"/>
+      <c r="I16" s="71"/>
+      <c r="J16" s="71"/>
+      <c r="K16" s="71"/>
+      <c r="L16" s="71"/>
+      <c r="M16" s="71"/>
+      <c r="N16" s="71"/>
+      <c r="O16" s="71"/>
+      <c r="P16" s="71"/>
+      <c r="Q16" s="71"/>
+      <c r="R16" s="71"/>
+      <c r="S16" s="71"/>
+      <c r="T16" s="71"/>
+      <c r="U16" s="72"/>
+    </row>
+    <row r="17" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="70"/>
+      <c r="B17" s="71"/>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="71"/>
+      <c r="F17" s="71"/>
+      <c r="G17" s="71"/>
+      <c r="H17" s="71"/>
+      <c r="I17" s="71"/>
+      <c r="J17" s="71"/>
+      <c r="K17" s="71"/>
+      <c r="L17" s="71"/>
+      <c r="M17" s="71"/>
+      <c r="N17" s="71"/>
+      <c r="O17" s="71"/>
+      <c r="P17" s="71"/>
+      <c r="Q17" s="71"/>
+      <c r="R17" s="71"/>
+      <c r="S17" s="71"/>
+      <c r="T17" s="71"/>
+      <c r="U17" s="72"/>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="27"/>
-      <c r="D18" s="27"/>
-      <c r="E18" s="27"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="27"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="27"/>
-      <c r="K18" s="27"/>
-      <c r="L18" s="27"/>
-      <c r="M18" s="27"/>
-      <c r="N18" s="27"/>
-      <c r="O18" s="27"/>
-      <c r="P18" s="27"/>
-      <c r="Q18" s="27"/>
-      <c r="R18" s="27"/>
-      <c r="S18" s="27"/>
-      <c r="T18" s="27"/>
-      <c r="U18" s="28"/>
-    </row>
-    <row r="19" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="71" t="s">
+      <c r="B18" s="26"/>
+      <c r="C18" s="26"/>
+      <c r="D18" s="26"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="26"/>
+      <c r="G18" s="26"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="26"/>
+      <c r="J18" s="26"/>
+      <c r="K18" s="26"/>
+      <c r="L18" s="26"/>
+      <c r="M18" s="26"/>
+      <c r="N18" s="26"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="26"/>
+      <c r="Q18" s="26"/>
+      <c r="R18" s="26"/>
+      <c r="S18" s="26"/>
+      <c r="T18" s="26"/>
+      <c r="U18" s="27"/>
+    </row>
+    <row r="19" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="70" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="72"/>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="72"/>
-      <c r="F19" s="72"/>
-      <c r="G19" s="72"/>
-      <c r="H19" s="72"/>
-      <c r="I19" s="72"/>
-      <c r="J19" s="72"/>
-      <c r="K19" s="72"/>
-      <c r="L19" s="72"/>
-      <c r="M19" s="72"/>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="72"/>
-      <c r="S19" s="72"/>
-      <c r="T19" s="72"/>
-      <c r="U19" s="73"/>
-    </row>
-    <row r="20" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="71"/>
-      <c r="B20" s="72"/>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="72"/>
-      <c r="F20" s="72"/>
-      <c r="G20" s="72"/>
-      <c r="H20" s="72"/>
-      <c r="I20" s="72"/>
-      <c r="J20" s="72"/>
-      <c r="K20" s="72"/>
-      <c r="L20" s="72"/>
-      <c r="M20" s="72"/>
-      <c r="N20" s="72"/>
-      <c r="O20" s="72"/>
-      <c r="P20" s="72"/>
-      <c r="Q20" s="72"/>
-      <c r="R20" s="72"/>
-      <c r="S20" s="72"/>
-      <c r="T20" s="72"/>
-      <c r="U20" s="73"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+      <c r="B19" s="71"/>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="71"/>
+      <c r="F19" s="71"/>
+      <c r="G19" s="71"/>
+      <c r="H19" s="71"/>
+      <c r="I19" s="71"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="71"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="71"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="71"/>
+      <c r="R19" s="71"/>
+      <c r="S19" s="71"/>
+      <c r="T19" s="71"/>
+      <c r="U19" s="72"/>
+    </row>
+    <row r="20" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="70"/>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="71"/>
+      <c r="G20" s="71"/>
+      <c r="H20" s="71"/>
+      <c r="I20" s="71"/>
+      <c r="J20" s="71"/>
+      <c r="K20" s="71"/>
+      <c r="L20" s="71"/>
+      <c r="M20" s="71"/>
+      <c r="N20" s="71"/>
+      <c r="O20" s="71"/>
+      <c r="P20" s="71"/>
+      <c r="Q20" s="71"/>
+      <c r="R20" s="71"/>
+      <c r="S20" s="71"/>
+      <c r="T20" s="71"/>
+      <c r="U20" s="72"/>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21" s="28" t="s">
         <v>144</v>
       </c>
-      <c r="B21" s="27"/>
-      <c r="C21" s="27"/>
-      <c r="D21" s="27"/>
-      <c r="E21" s="27"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="27"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="27"/>
-      <c r="K21" s="27"/>
-      <c r="L21" s="27"/>
-      <c r="M21" s="27"/>
-      <c r="N21" s="27"/>
-      <c r="O21" s="27"/>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="27"/>
-      <c r="R21" s="27"/>
-      <c r="S21" s="27"/>
-      <c r="T21" s="27"/>
-      <c r="U21" s="28"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="29"/>
-      <c r="B22" s="27"/>
-      <c r="C22" s="27"/>
-      <c r="D22" s="27"/>
-      <c r="E22" s="27"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="N22" s="27"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="27"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="27"/>
-      <c r="U22" s="28"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="30"/>
-      <c r="B23" s="27"/>
-      <c r="C23" s="27"/>
-      <c r="D23" s="27"/>
-      <c r="E23" s="27"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="27"/>
-      <c r="H23" s="27"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="27"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="N23" s="27"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="27"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="27"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="27"/>
-      <c r="U23" s="28"/>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26"/>
+      <c r="H21" s="26"/>
+      <c r="I21" s="26"/>
+      <c r="J21" s="26"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="26"/>
+      <c r="M21" s="26"/>
+      <c r="N21" s="26"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="26"/>
+      <c r="Q21" s="26"/>
+      <c r="R21" s="26"/>
+      <c r="S21" s="26"/>
+      <c r="T21" s="26"/>
+      <c r="U21" s="27"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22" s="28"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
+      <c r="H22" s="26"/>
+      <c r="I22" s="26"/>
+      <c r="J22" s="26"/>
+      <c r="K22" s="26"/>
+      <c r="L22" s="26"/>
+      <c r="M22" s="26"/>
+      <c r="N22" s="26"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="26"/>
+      <c r="Q22" s="26"/>
+      <c r="R22" s="26"/>
+      <c r="S22" s="26"/>
+      <c r="T22" s="26"/>
+      <c r="U22" s="27"/>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23" s="29"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26"/>
+      <c r="H23" s="26"/>
+      <c r="I23" s="26"/>
+      <c r="J23" s="26"/>
+      <c r="K23" s="26"/>
+      <c r="L23" s="26"/>
+      <c r="M23" s="26"/>
+      <c r="N23" s="26"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="26"/>
+      <c r="Q23" s="26"/>
+      <c r="R23" s="26"/>
+      <c r="S23" s="26"/>
+      <c r="T23" s="26"/>
+      <c r="U23" s="27"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="27"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="27"/>
-      <c r="R24" s="27"/>
-      <c r="S24" s="27"/>
-      <c r="T24" s="27"/>
-      <c r="U24" s="28"/>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A25" s="30" t="s">
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="26"/>
+      <c r="I24" s="26"/>
+      <c r="J24" s="26"/>
+      <c r="K24" s="26"/>
+      <c r="L24" s="26"/>
+      <c r="M24" s="26"/>
+      <c r="N24" s="26"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="26"/>
+      <c r="Q24" s="26"/>
+      <c r="R24" s="26"/>
+      <c r="S24" s="26"/>
+      <c r="T24" s="26"/>
+      <c r="U24" s="27"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25" s="29" t="s">
         <v>182</v>
       </c>
-      <c r="B25" s="27"/>
-      <c r="C25" s="27"/>
-      <c r="D25" s="27"/>
-      <c r="E25" s="27"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="27"/>
-      <c r="H25" s="27"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="27"/>
-      <c r="K25" s="27"/>
-      <c r="L25" s="27"/>
-      <c r="M25" s="27"/>
-      <c r="N25" s="27"/>
-      <c r="O25" s="27"/>
-      <c r="P25" s="27"/>
-      <c r="Q25" s="27"/>
-      <c r="R25" s="27"/>
-      <c r="S25" s="27"/>
-      <c r="T25" s="27"/>
-      <c r="U25" s="28"/>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="26"/>
+      <c r="I25" s="26"/>
+      <c r="J25" s="26"/>
+      <c r="K25" s="26"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="26"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="26"/>
+      <c r="R25" s="26"/>
+      <c r="S25" s="26"/>
+      <c r="T25" s="26"/>
+      <c r="U25" s="27"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="H26" s="27"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
-      <c r="P26" s="27"/>
-      <c r="Q26" s="27"/>
-      <c r="R26" s="27"/>
-      <c r="S26" s="27"/>
-      <c r="T26" s="27"/>
-      <c r="U26" s="28"/>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+      <c r="B26" s="26"/>
+      <c r="C26" s="26"/>
+      <c r="D26" s="26"/>
+      <c r="E26" s="26"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="26"/>
+      <c r="I26" s="26"/>
+      <c r="J26" s="26"/>
+      <c r="K26" s="26"/>
+      <c r="L26" s="26"/>
+      <c r="M26" s="26"/>
+      <c r="N26" s="26"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="26"/>
+      <c r="Q26" s="26"/>
+      <c r="R26" s="26"/>
+      <c r="S26" s="26"/>
+      <c r="T26" s="26"/>
+      <c r="U26" s="27"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27" s="29" t="s">
         <v>184</v>
       </c>
-      <c r="B27" s="27"/>
-      <c r="C27" s="27"/>
-      <c r="D27" s="27"/>
-      <c r="E27" s="27"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="27"/>
-      <c r="H27" s="27"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="27"/>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
-      <c r="N27" s="27"/>
-      <c r="O27" s="27"/>
-      <c r="P27" s="27"/>
-      <c r="Q27" s="27"/>
-      <c r="R27" s="27"/>
-      <c r="S27" s="27"/>
-      <c r="T27" s="27"/>
-      <c r="U27" s="28"/>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="26"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="26"/>
+      <c r="K27" s="26"/>
+      <c r="L27" s="26"/>
+      <c r="M27" s="26"/>
+      <c r="N27" s="26"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="26"/>
+      <c r="Q27" s="26"/>
+      <c r="R27" s="26"/>
+      <c r="S27" s="26"/>
+      <c r="T27" s="26"/>
+      <c r="U27" s="27"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="B28" s="27"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="27"/>
-      <c r="E28" s="27"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="27"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="27"/>
-      <c r="K28" s="27"/>
-      <c r="L28" s="27"/>
-      <c r="M28" s="27"/>
-      <c r="N28" s="27"/>
-      <c r="O28" s="27"/>
-      <c r="P28" s="27"/>
-      <c r="Q28" s="27"/>
-      <c r="R28" s="27"/>
-      <c r="S28" s="27"/>
-      <c r="T28" s="27"/>
-      <c r="U28" s="28"/>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="26"/>
+      <c r="J28" s="26"/>
+      <c r="K28" s="26"/>
+      <c r="L28" s="26"/>
+      <c r="M28" s="26"/>
+      <c r="N28" s="26"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="26"/>
+      <c r="Q28" s="26"/>
+      <c r="R28" s="26"/>
+      <c r="S28" s="26"/>
+      <c r="T28" s="26"/>
+      <c r="U28" s="27"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29" s="29" t="s">
         <v>186</v>
       </c>
-      <c r="B29" s="27"/>
-      <c r="C29" s="27"/>
-      <c r="D29" s="27"/>
-      <c r="E29" s="27"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="27"/>
-      <c r="H29" s="27"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="27"/>
-      <c r="K29" s="27"/>
-      <c r="L29" s="27"/>
-      <c r="M29" s="27"/>
-      <c r="N29" s="27"/>
-      <c r="O29" s="27"/>
-      <c r="P29" s="27"/>
-      <c r="Q29" s="27"/>
-      <c r="R29" s="27"/>
-      <c r="S29" s="27"/>
-      <c r="T29" s="27"/>
-      <c r="U29" s="28"/>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+      <c r="B29" s="26"/>
+      <c r="C29" s="26"/>
+      <c r="D29" s="26"/>
+      <c r="E29" s="26"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="26"/>
+      <c r="I29" s="26"/>
+      <c r="J29" s="26"/>
+      <c r="K29" s="26"/>
+      <c r="L29" s="26"/>
+      <c r="M29" s="26"/>
+      <c r="N29" s="26"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="26"/>
+      <c r="Q29" s="26"/>
+      <c r="R29" s="26"/>
+      <c r="S29" s="26"/>
+      <c r="T29" s="26"/>
+      <c r="U29" s="27"/>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="27"/>
-      <c r="C30" s="27"/>
-      <c r="D30" s="27"/>
-      <c r="E30" s="27"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="27"/>
-      <c r="H30" s="27"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="27"/>
-      <c r="K30" s="27"/>
-      <c r="L30" s="27"/>
-      <c r="M30" s="27"/>
-      <c r="N30" s="27"/>
-      <c r="O30" s="27"/>
-      <c r="P30" s="27"/>
-      <c r="Q30" s="27"/>
-      <c r="R30" s="27"/>
-      <c r="S30" s="27"/>
-      <c r="T30" s="27"/>
-      <c r="U30" s="28"/>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A31" s="30" t="s">
+      <c r="B30" s="26"/>
+      <c r="C30" s="26"/>
+      <c r="D30" s="26"/>
+      <c r="E30" s="26"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
+      <c r="H30" s="26"/>
+      <c r="I30" s="26"/>
+      <c r="J30" s="26"/>
+      <c r="K30" s="26"/>
+      <c r="L30" s="26"/>
+      <c r="M30" s="26"/>
+      <c r="N30" s="26"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="26"/>
+      <c r="Q30" s="26"/>
+      <c r="R30" s="26"/>
+      <c r="S30" s="26"/>
+      <c r="T30" s="26"/>
+      <c r="U30" s="27"/>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A31" s="29" t="s">
         <v>188</v>
       </c>
-      <c r="B31" s="27"/>
-      <c r="C31" s="27"/>
-      <c r="D31" s="27"/>
-      <c r="E31" s="27"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="27"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="27"/>
-      <c r="K31" s="27"/>
-      <c r="L31" s="27"/>
-      <c r="M31" s="27"/>
-      <c r="N31" s="27"/>
-      <c r="O31" s="27"/>
-      <c r="P31" s="27"/>
-      <c r="Q31" s="27"/>
-      <c r="R31" s="27"/>
-      <c r="S31" s="27"/>
-      <c r="T31" s="27"/>
-      <c r="U31" s="28"/>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A32" s="30"/>
-      <c r="B32" s="27"/>
-      <c r="C32" s="27"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="27"/>
-      <c r="H32" s="27"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="27"/>
-      <c r="K32" s="27"/>
-      <c r="L32" s="27"/>
-      <c r="M32" s="27"/>
-      <c r="N32" s="27"/>
-      <c r="O32" s="27"/>
-      <c r="P32" s="27"/>
-      <c r="Q32" s="27"/>
-      <c r="R32" s="27"/>
-      <c r="S32" s="27"/>
-      <c r="T32" s="27"/>
-      <c r="U32" s="28"/>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A33" s="30"/>
-      <c r="B33" s="27"/>
-      <c r="C33" s="27"/>
-      <c r="D33" s="27"/>
-      <c r="E33" s="27"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="27"/>
-      <c r="H33" s="27"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="27"/>
-      <c r="K33" s="27"/>
-      <c r="L33" s="27"/>
-      <c r="M33" s="27"/>
-      <c r="N33" s="27"/>
-      <c r="O33" s="27"/>
-      <c r="P33" s="27"/>
-      <c r="Q33" s="27"/>
-      <c r="R33" s="27"/>
-      <c r="S33" s="27"/>
-      <c r="T33" s="27"/>
-      <c r="U33" s="28"/>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A34" s="40" t="s">
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
+      <c r="D31" s="26"/>
+      <c r="E31" s="26"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
+      <c r="H31" s="26"/>
+      <c r="I31" s="26"/>
+      <c r="J31" s="26"/>
+      <c r="K31" s="26"/>
+      <c r="L31" s="26"/>
+      <c r="M31" s="26"/>
+      <c r="N31" s="26"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="26"/>
+      <c r="Q31" s="26"/>
+      <c r="R31" s="26"/>
+      <c r="S31" s="26"/>
+      <c r="T31" s="26"/>
+      <c r="U31" s="27"/>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A32" s="29"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="26"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
+      <c r="H32" s="26"/>
+      <c r="I32" s="26"/>
+      <c r="J32" s="26"/>
+      <c r="K32" s="26"/>
+      <c r="L32" s="26"/>
+      <c r="M32" s="26"/>
+      <c r="N32" s="26"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="26"/>
+      <c r="Q32" s="26"/>
+      <c r="R32" s="26"/>
+      <c r="S32" s="26"/>
+      <c r="T32" s="26"/>
+      <c r="U32" s="27"/>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A33" s="29"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="26"/>
+      <c r="D33" s="26"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
+      <c r="H33" s="26"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="26"/>
+      <c r="K33" s="26"/>
+      <c r="L33" s="26"/>
+      <c r="M33" s="26"/>
+      <c r="N33" s="26"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="26"/>
+      <c r="Q33" s="26"/>
+      <c r="R33" s="26"/>
+      <c r="S33" s="26"/>
+      <c r="T33" s="26"/>
+      <c r="U33" s="27"/>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A34" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B34" s="27"/>
-      <c r="C34" s="27"/>
-      <c r="D34" s="27"/>
-      <c r="E34" s="27"/>
-      <c r="F34" s="27"/>
-      <c r="G34" s="27"/>
-      <c r="H34" s="27"/>
-      <c r="I34" s="27"/>
-      <c r="J34" s="27"/>
-      <c r="K34" s="27"/>
-      <c r="L34" s="27"/>
-      <c r="M34" s="27"/>
-      <c r="N34" s="27"/>
-      <c r="O34" s="27"/>
-      <c r="P34" s="27"/>
-      <c r="Q34" s="27"/>
-      <c r="R34" s="27"/>
-      <c r="S34" s="27"/>
-      <c r="T34" s="27"/>
-      <c r="U34" s="28"/>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A35" s="42" t="s">
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
+      <c r="D34" s="26"/>
+      <c r="E34" s="26"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
+      <c r="H34" s="26"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="26"/>
+      <c r="K34" s="26"/>
+      <c r="L34" s="26"/>
+      <c r="M34" s="26"/>
+      <c r="N34" s="26"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="26"/>
+      <c r="Q34" s="26"/>
+      <c r="R34" s="26"/>
+      <c r="S34" s="26"/>
+      <c r="T34" s="26"/>
+      <c r="U34" s="27"/>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A35" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="B35" s="27"/>
-      <c r="C35" s="27"/>
-      <c r="D35" s="27"/>
-      <c r="E35" s="27"/>
-      <c r="F35" s="27"/>
-      <c r="G35" s="27"/>
-      <c r="H35" s="27"/>
-      <c r="I35" s="27"/>
-      <c r="J35" s="27"/>
-      <c r="K35" s="27"/>
-      <c r="L35" s="27"/>
-      <c r="M35" s="27"/>
-      <c r="N35" s="27"/>
-      <c r="O35" s="27"/>
-      <c r="P35" s="27"/>
-      <c r="Q35" s="27"/>
-      <c r="R35" s="27"/>
-      <c r="S35" s="27"/>
-      <c r="T35" s="27"/>
-      <c r="U35" s="28"/>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="30" t="s">
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
+      <c r="D35" s="26"/>
+      <c r="E35" s="26"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
+      <c r="H35" s="26"/>
+      <c r="I35" s="26"/>
+      <c r="J35" s="26"/>
+      <c r="K35" s="26"/>
+      <c r="L35" s="26"/>
+      <c r="M35" s="26"/>
+      <c r="N35" s="26"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="26"/>
+      <c r="Q35" s="26"/>
+      <c r="R35" s="26"/>
+      <c r="S35" s="26"/>
+      <c r="T35" s="26"/>
+      <c r="U35" s="27"/>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A36" s="29" t="s">
         <v>195</v>
       </c>
-      <c r="B36" s="27"/>
-      <c r="C36" s="27"/>
-      <c r="D36" s="27"/>
-      <c r="E36" s="27"/>
-      <c r="F36" s="27"/>
-      <c r="G36" s="27"/>
-      <c r="H36" s="27"/>
-      <c r="I36" s="27"/>
-      <c r="J36" s="27"/>
-      <c r="K36" s="27"/>
-      <c r="L36" s="27"/>
-      <c r="M36" s="27"/>
-      <c r="N36" s="27"/>
-      <c r="O36" s="27"/>
-      <c r="P36" s="27"/>
-      <c r="Q36" s="27"/>
-      <c r="R36" s="27"/>
-      <c r="S36" s="27"/>
-      <c r="T36" s="27"/>
-      <c r="U36" s="28"/>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="30" t="s">
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
+      <c r="D36" s="26"/>
+      <c r="E36" s="26"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
+      <c r="H36" s="26"/>
+      <c r="I36" s="26"/>
+      <c r="J36" s="26"/>
+      <c r="K36" s="26"/>
+      <c r="L36" s="26"/>
+      <c r="M36" s="26"/>
+      <c r="N36" s="26"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="26"/>
+      <c r="Q36" s="26"/>
+      <c r="R36" s="26"/>
+      <c r="S36" s="26"/>
+      <c r="T36" s="26"/>
+      <c r="U36" s="27"/>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A37" s="29" t="s">
         <v>196</v>
       </c>
-      <c r="B37" s="27"/>
-      <c r="C37" s="27"/>
-      <c r="D37" s="27"/>
-      <c r="E37" s="27"/>
-      <c r="F37" s="27"/>
-      <c r="G37" s="27"/>
-      <c r="H37" s="27"/>
-      <c r="I37" s="27"/>
-      <c r="J37" s="27"/>
-      <c r="K37" s="27"/>
-      <c r="L37" s="27"/>
-      <c r="M37" s="27"/>
-      <c r="N37" s="27"/>
-      <c r="O37" s="27"/>
-      <c r="P37" s="27"/>
-      <c r="Q37" s="27"/>
-      <c r="R37" s="27"/>
-      <c r="S37" s="27"/>
-      <c r="T37" s="27"/>
-      <c r="U37" s="28"/>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A38" s="30" t="s">
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
+      <c r="D37" s="26"/>
+      <c r="E37" s="26"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="26"/>
+      <c r="I37" s="26"/>
+      <c r="J37" s="26"/>
+      <c r="K37" s="26"/>
+      <c r="L37" s="26"/>
+      <c r="M37" s="26"/>
+      <c r="N37" s="26"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="26"/>
+      <c r="Q37" s="26"/>
+      <c r="R37" s="26"/>
+      <c r="S37" s="26"/>
+      <c r="T37" s="26"/>
+      <c r="U37" s="27"/>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A38" s="29" t="s">
         <v>189</v>
       </c>
-      <c r="B38" s="27"/>
-      <c r="C38" s="27"/>
-      <c r="D38" s="27"/>
-      <c r="E38" s="27"/>
-      <c r="F38" s="27"/>
-      <c r="G38" s="27"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="27"/>
-      <c r="J38" s="27"/>
-      <c r="K38" s="27"/>
-      <c r="L38" s="27"/>
-      <c r="M38" s="27"/>
-      <c r="N38" s="27"/>
-      <c r="O38" s="27"/>
-      <c r="P38" s="27"/>
-      <c r="Q38" s="27"/>
-      <c r="R38" s="27"/>
-      <c r="S38" s="27"/>
-      <c r="T38" s="27"/>
-      <c r="U38" s="28"/>
-    </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A39" s="30" t="s">
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="26"/>
+      <c r="I38" s="26"/>
+      <c r="J38" s="26"/>
+      <c r="K38" s="26"/>
+      <c r="L38" s="26"/>
+      <c r="M38" s="26"/>
+      <c r="N38" s="26"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="26"/>
+      <c r="Q38" s="26"/>
+      <c r="R38" s="26"/>
+      <c r="S38" s="26"/>
+      <c r="T38" s="26"/>
+      <c r="U38" s="27"/>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A39" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="B39" s="27"/>
-      <c r="C39" s="27"/>
-      <c r="D39" s="27"/>
-      <c r="E39" s="27"/>
-      <c r="F39" s="27"/>
-      <c r="G39" s="27"/>
-      <c r="H39" s="27"/>
-      <c r="I39" s="27"/>
-      <c r="J39" s="27"/>
-      <c r="K39" s="27"/>
-      <c r="L39" s="27"/>
-      <c r="M39" s="27"/>
-      <c r="N39" s="27"/>
-      <c r="O39" s="27"/>
-      <c r="P39" s="27"/>
-      <c r="Q39" s="27"/>
-      <c r="R39" s="27"/>
-      <c r="S39" s="27"/>
-      <c r="T39" s="27"/>
-      <c r="U39" s="28"/>
-    </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A40" s="30" t="s">
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="D39" s="26"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+      <c r="N39" s="26"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="26"/>
+      <c r="Q39" s="26"/>
+      <c r="R39" s="26"/>
+      <c r="S39" s="26"/>
+      <c r="T39" s="26"/>
+      <c r="U39" s="27"/>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A40" s="29" t="s">
         <v>198</v>
       </c>
-      <c r="B40" s="27"/>
-      <c r="C40" s="27"/>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27"/>
-      <c r="F40" s="27"/>
-      <c r="G40" s="27"/>
-      <c r="H40" s="27"/>
-      <c r="I40" s="27"/>
-      <c r="J40" s="27"/>
-      <c r="K40" s="27"/>
-      <c r="L40" s="27"/>
-      <c r="M40" s="27"/>
-      <c r="N40" s="27"/>
-      <c r="O40" s="27"/>
-      <c r="P40" s="27"/>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="27"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="27"/>
-      <c r="U40" s="28"/>
-    </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A41" s="30"/>
-      <c r="B41" s="27"/>
-      <c r="C41" s="27"/>
-      <c r="D41" s="27"/>
-      <c r="E41" s="27"/>
-      <c r="F41" s="27"/>
-      <c r="G41" s="27"/>
-      <c r="H41" s="27"/>
-      <c r="I41" s="27"/>
-      <c r="J41" s="27"/>
-      <c r="K41" s="27"/>
-      <c r="L41" s="27"/>
-      <c r="M41" s="27"/>
-      <c r="N41" s="27"/>
-      <c r="O41" s="27"/>
-      <c r="P41" s="27"/>
-      <c r="Q41" s="27"/>
-      <c r="R41" s="27"/>
-      <c r="S41" s="27"/>
-      <c r="T41" s="27"/>
-      <c r="U41" s="28"/>
-    </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A42" s="30"/>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="H42" s="27"/>
-      <c r="I42" s="27"/>
-      <c r="J42" s="27"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
-      <c r="P42" s="27"/>
-      <c r="Q42" s="27"/>
-      <c r="R42" s="27"/>
-      <c r="S42" s="27"/>
-      <c r="T42" s="27"/>
-      <c r="U42" s="28"/>
-    </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A43" s="25" t="s">
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="D40" s="26"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="26"/>
+      <c r="P40" s="26"/>
+      <c r="Q40" s="26"/>
+      <c r="R40" s="26"/>
+      <c r="S40" s="26"/>
+      <c r="T40" s="26"/>
+      <c r="U40" s="27"/>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A41" s="29"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="26"/>
+      <c r="K41" s="26"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="26"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="26"/>
+      <c r="S41" s="26"/>
+      <c r="T41" s="26"/>
+      <c r="U41" s="27"/>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A42" s="29"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="M42" s="26"/>
+      <c r="N42" s="26"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="R42" s="26"/>
+      <c r="S42" s="26"/>
+      <c r="T42" s="26"/>
+      <c r="U42" s="27"/>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A43" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="B43" s="27"/>
-      <c r="C43" s="27"/>
-      <c r="D43" s="27"/>
-      <c r="E43" s="27"/>
-      <c r="F43" s="27"/>
-      <c r="G43" s="27"/>
-      <c r="H43" s="27"/>
-      <c r="I43" s="27"/>
-      <c r="J43" s="27"/>
-      <c r="K43" s="27"/>
-      <c r="L43" s="27"/>
-      <c r="M43" s="27"/>
-      <c r="N43" s="27"/>
-      <c r="O43" s="27"/>
-      <c r="P43" s="27"/>
-      <c r="Q43" s="27"/>
-      <c r="R43" s="27"/>
-      <c r="S43" s="27"/>
-      <c r="T43" s="27"/>
-      <c r="U43" s="28"/>
-    </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A44" s="41" t="s">
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="26"/>
+      <c r="I43" s="26"/>
+      <c r="J43" s="26"/>
+      <c r="K43" s="26"/>
+      <c r="L43" s="26"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="26"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="26"/>
+      <c r="R43" s="26"/>
+      <c r="S43" s="26"/>
+      <c r="T43" s="26"/>
+      <c r="U43" s="27"/>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A44" s="39" t="s">
         <v>207</v>
       </c>
-      <c r="B44" s="27"/>
-      <c r="C44" s="27"/>
-      <c r="D44" s="27"/>
-      <c r="E44" s="27"/>
-      <c r="F44" s="27"/>
-      <c r="G44" s="27"/>
-      <c r="H44" s="27"/>
-      <c r="I44" s="27"/>
-      <c r="J44" s="27"/>
-      <c r="K44" s="27"/>
-      <c r="L44" s="27"/>
-      <c r="M44" s="27"/>
-      <c r="N44" s="27"/>
-      <c r="O44" s="27"/>
-      <c r="P44" s="27"/>
-      <c r="Q44" s="27"/>
-      <c r="R44" s="27"/>
-      <c r="S44" s="27"/>
-      <c r="T44" s="27"/>
-      <c r="U44" s="28"/>
-    </row>
-    <row r="45" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="74" t="s">
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="26"/>
+      <c r="I44" s="26"/>
+      <c r="J44" s="26"/>
+      <c r="K44" s="26"/>
+      <c r="L44" s="26"/>
+      <c r="M44" s="26"/>
+      <c r="N44" s="26"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="26"/>
+      <c r="Q44" s="26"/>
+      <c r="R44" s="26"/>
+      <c r="S44" s="26"/>
+      <c r="T44" s="26"/>
+      <c r="U44" s="27"/>
+    </row>
+    <row r="45" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="67" t="s">
         <v>223</v>
       </c>
-      <c r="B45" s="75"/>
-      <c r="C45" s="75"/>
-      <c r="D45" s="75"/>
-      <c r="E45" s="75"/>
-      <c r="F45" s="75"/>
-      <c r="G45" s="75"/>
-      <c r="H45" s="75"/>
-      <c r="I45" s="75"/>
-      <c r="J45" s="75"/>
-      <c r="K45" s="75"/>
-      <c r="L45" s="75"/>
-      <c r="M45" s="75"/>
-      <c r="N45" s="75"/>
-      <c r="O45" s="75"/>
-      <c r="P45" s="75"/>
-      <c r="Q45" s="75"/>
-      <c r="R45" s="75"/>
-      <c r="S45" s="75"/>
-      <c r="T45" s="75"/>
-      <c r="U45" s="76"/>
-    </row>
-    <row r="46" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="74"/>
-      <c r="B46" s="75"/>
-      <c r="C46" s="75"/>
-      <c r="D46" s="75"/>
-      <c r="E46" s="75"/>
-      <c r="F46" s="75"/>
-      <c r="G46" s="75"/>
-      <c r="H46" s="75"/>
-      <c r="I46" s="75"/>
-      <c r="J46" s="75"/>
-      <c r="K46" s="75"/>
-      <c r="L46" s="75"/>
-      <c r="M46" s="75"/>
-      <c r="N46" s="75"/>
-      <c r="O46" s="75"/>
-      <c r="P46" s="75"/>
-      <c r="Q46" s="75"/>
-      <c r="R46" s="75"/>
-      <c r="S46" s="75"/>
-      <c r="T46" s="75"/>
-      <c r="U46" s="76"/>
-    </row>
-    <row r="47" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="74"/>
-      <c r="B47" s="75"/>
-      <c r="C47" s="75"/>
-      <c r="D47" s="75"/>
-      <c r="E47" s="75"/>
-      <c r="F47" s="75"/>
-      <c r="G47" s="75"/>
-      <c r="H47" s="75"/>
-      <c r="I47" s="75"/>
-      <c r="J47" s="75"/>
-      <c r="K47" s="75"/>
-      <c r="L47" s="75"/>
-      <c r="M47" s="75"/>
-      <c r="N47" s="75"/>
-      <c r="O47" s="75"/>
-      <c r="P47" s="75"/>
-      <c r="Q47" s="75"/>
-      <c r="R47" s="75"/>
-      <c r="S47" s="75"/>
-      <c r="T47" s="75"/>
-      <c r="U47" s="76"/>
-    </row>
-    <row r="48" spans="1:21" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="74"/>
-      <c r="B48" s="75"/>
-      <c r="C48" s="75"/>
-      <c r="D48" s="75"/>
-      <c r="E48" s="75"/>
-      <c r="F48" s="75"/>
-      <c r="G48" s="75"/>
-      <c r="H48" s="75"/>
-      <c r="I48" s="75"/>
-      <c r="J48" s="75"/>
-      <c r="K48" s="75"/>
-      <c r="L48" s="75"/>
-      <c r="M48" s="75"/>
-      <c r="N48" s="75"/>
-      <c r="O48" s="75"/>
-      <c r="P48" s="75"/>
-      <c r="Q48" s="75"/>
-      <c r="R48" s="75"/>
-      <c r="S48" s="75"/>
-      <c r="T48" s="75"/>
-      <c r="U48" s="76"/>
-    </row>
-    <row r="49" spans="1:21" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="74"/>
-      <c r="B49" s="75"/>
-      <c r="C49" s="75"/>
-      <c r="D49" s="75"/>
-      <c r="E49" s="75"/>
-      <c r="F49" s="75"/>
-      <c r="G49" s="75"/>
-      <c r="H49" s="75"/>
-      <c r="I49" s="75"/>
-      <c r="J49" s="75"/>
-      <c r="K49" s="75"/>
-      <c r="L49" s="75"/>
-      <c r="M49" s="75"/>
-      <c r="N49" s="75"/>
-      <c r="O49" s="75"/>
-      <c r="P49" s="75"/>
-      <c r="Q49" s="75"/>
-      <c r="R49" s="75"/>
-      <c r="S49" s="75"/>
-      <c r="T49" s="75"/>
-      <c r="U49" s="76"/>
-    </row>
-    <row r="50" spans="1:21" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="74" t="s">
+      <c r="B45" s="68"/>
+      <c r="C45" s="68"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
+      <c r="H45" s="68"/>
+      <c r="I45" s="68"/>
+      <c r="J45" s="68"/>
+      <c r="K45" s="68"/>
+      <c r="L45" s="68"/>
+      <c r="M45" s="68"/>
+      <c r="N45" s="68"/>
+      <c r="O45" s="68"/>
+      <c r="P45" s="68"/>
+      <c r="Q45" s="68"/>
+      <c r="R45" s="68"/>
+      <c r="S45" s="68"/>
+      <c r="T45" s="68"/>
+      <c r="U45" s="69"/>
+    </row>
+    <row r="46" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="67"/>
+      <c r="B46" s="68"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="68"/>
+      <c r="J46" s="68"/>
+      <c r="K46" s="68"/>
+      <c r="L46" s="68"/>
+      <c r="M46" s="68"/>
+      <c r="N46" s="68"/>
+      <c r="O46" s="68"/>
+      <c r="P46" s="68"/>
+      <c r="Q46" s="68"/>
+      <c r="R46" s="68"/>
+      <c r="S46" s="68"/>
+      <c r="T46" s="68"/>
+      <c r="U46" s="69"/>
+    </row>
+    <row r="47" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="67"/>
+      <c r="B47" s="68"/>
+      <c r="C47" s="68"/>
+      <c r="D47" s="68"/>
+      <c r="E47" s="68"/>
+      <c r="F47" s="68"/>
+      <c r="G47" s="68"/>
+      <c r="H47" s="68"/>
+      <c r="I47" s="68"/>
+      <c r="J47" s="68"/>
+      <c r="K47" s="68"/>
+      <c r="L47" s="68"/>
+      <c r="M47" s="68"/>
+      <c r="N47" s="68"/>
+      <c r="O47" s="68"/>
+      <c r="P47" s="68"/>
+      <c r="Q47" s="68"/>
+      <c r="R47" s="68"/>
+      <c r="S47" s="68"/>
+      <c r="T47" s="68"/>
+      <c r="U47" s="69"/>
+    </row>
+    <row r="48" spans="1:21" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="67"/>
+      <c r="B48" s="68"/>
+      <c r="C48" s="68"/>
+      <c r="D48" s="68"/>
+      <c r="E48" s="68"/>
+      <c r="F48" s="68"/>
+      <c r="G48" s="68"/>
+      <c r="H48" s="68"/>
+      <c r="I48" s="68"/>
+      <c r="J48" s="68"/>
+      <c r="K48" s="68"/>
+      <c r="L48" s="68"/>
+      <c r="M48" s="68"/>
+      <c r="N48" s="68"/>
+      <c r="O48" s="68"/>
+      <c r="P48" s="68"/>
+      <c r="Q48" s="68"/>
+      <c r="R48" s="68"/>
+      <c r="S48" s="68"/>
+      <c r="T48" s="68"/>
+      <c r="U48" s="69"/>
+    </row>
+    <row r="49" spans="1:21" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="67"/>
+      <c r="B49" s="68"/>
+      <c r="C49" s="68"/>
+      <c r="D49" s="68"/>
+      <c r="E49" s="68"/>
+      <c r="F49" s="68"/>
+      <c r="G49" s="68"/>
+      <c r="H49" s="68"/>
+      <c r="I49" s="68"/>
+      <c r="J49" s="68"/>
+      <c r="K49" s="68"/>
+      <c r="L49" s="68"/>
+      <c r="M49" s="68"/>
+      <c r="N49" s="68"/>
+      <c r="O49" s="68"/>
+      <c r="P49" s="68"/>
+      <c r="Q49" s="68"/>
+      <c r="R49" s="68"/>
+      <c r="S49" s="68"/>
+      <c r="T49" s="68"/>
+      <c r="U49" s="69"/>
+    </row>
+    <row r="50" spans="1:21" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="67" t="s">
         <v>146</v>
       </c>
-      <c r="B50" s="75"/>
-      <c r="C50" s="75"/>
-      <c r="D50" s="75"/>
-      <c r="E50" s="75"/>
-      <c r="F50" s="75"/>
-      <c r="G50" s="75"/>
-      <c r="H50" s="75"/>
-      <c r="I50" s="75"/>
-      <c r="J50" s="75"/>
-      <c r="K50" s="75"/>
-      <c r="L50" s="75"/>
-      <c r="M50" s="75"/>
-      <c r="N50" s="75"/>
-      <c r="O50" s="75"/>
-      <c r="P50" s="75"/>
-      <c r="Q50" s="75"/>
-      <c r="R50" s="75"/>
-      <c r="S50" s="75"/>
-      <c r="T50" s="75"/>
-      <c r="U50" s="76"/>
-    </row>
-    <row r="51" spans="1:21" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="74"/>
-      <c r="B51" s="75"/>
-      <c r="C51" s="75"/>
-      <c r="D51" s="75"/>
-      <c r="E51" s="75"/>
-      <c r="F51" s="75"/>
-      <c r="G51" s="75"/>
-      <c r="H51" s="75"/>
-      <c r="I51" s="75"/>
-      <c r="J51" s="75"/>
-      <c r="K51" s="75"/>
-      <c r="L51" s="75"/>
-      <c r="M51" s="75"/>
-      <c r="N51" s="75"/>
-      <c r="O51" s="75"/>
-      <c r="P51" s="75"/>
-      <c r="Q51" s="75"/>
-      <c r="R51" s="75"/>
-      <c r="S51" s="75"/>
-      <c r="T51" s="75"/>
-      <c r="U51" s="76"/>
-    </row>
-    <row r="52" spans="1:21" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="74"/>
-      <c r="B52" s="75"/>
-      <c r="C52" s="75"/>
-      <c r="D52" s="75"/>
-      <c r="E52" s="75"/>
-      <c r="F52" s="75"/>
-      <c r="G52" s="75"/>
-      <c r="H52" s="75"/>
-      <c r="I52" s="75"/>
-      <c r="J52" s="75"/>
-      <c r="K52" s="75"/>
-      <c r="L52" s="75"/>
-      <c r="M52" s="75"/>
-      <c r="N52" s="75"/>
-      <c r="O52" s="75"/>
-      <c r="P52" s="75"/>
-      <c r="Q52" s="75"/>
-      <c r="R52" s="75"/>
-      <c r="S52" s="75"/>
-      <c r="T52" s="75"/>
-      <c r="U52" s="76"/>
-    </row>
-    <row r="53" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="74"/>
-      <c r="B53" s="75"/>
-      <c r="C53" s="75"/>
-      <c r="D53" s="75"/>
-      <c r="E53" s="75"/>
-      <c r="F53" s="75"/>
-      <c r="G53" s="75"/>
-      <c r="H53" s="75"/>
-      <c r="I53" s="75"/>
-      <c r="J53" s="75"/>
-      <c r="K53" s="75"/>
-      <c r="L53" s="75"/>
-      <c r="M53" s="75"/>
-      <c r="N53" s="75"/>
-      <c r="O53" s="75"/>
-      <c r="P53" s="75"/>
-      <c r="Q53" s="75"/>
-      <c r="R53" s="75"/>
-      <c r="S53" s="75"/>
-      <c r="T53" s="75"/>
-      <c r="U53" s="76"/>
-    </row>
-    <row r="54" spans="1:21" ht="12.45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="32"/>
-      <c r="B54" s="33"/>
-      <c r="C54" s="33"/>
-      <c r="D54" s="33"/>
-      <c r="E54" s="33"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="33"/>
-      <c r="H54" s="33"/>
-      <c r="I54" s="33"/>
-      <c r="J54" s="33"/>
-      <c r="K54" s="33"/>
-      <c r="L54" s="33"/>
-      <c r="M54" s="33"/>
-      <c r="N54" s="33"/>
-      <c r="O54" s="33"/>
-      <c r="P54" s="33"/>
-      <c r="Q54" s="33"/>
-      <c r="R54" s="33"/>
-      <c r="S54" s="33"/>
-      <c r="T54" s="33"/>
-      <c r="U54" s="34"/>
-    </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1"/>
-      <c r="S55" s="1"/>
-      <c r="T55" s="1"/>
-      <c r="U55" s="1"/>
-    </row>
-    <row r="56" spans="1:21" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1"/>
-      <c r="S56" s="1"/>
-      <c r="T56" s="1"/>
-      <c r="U56" s="1"/>
-    </row>
-    <row r="57" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="77" t="s">
+      <c r="B50" s="68"/>
+      <c r="C50" s="68"/>
+      <c r="D50" s="68"/>
+      <c r="E50" s="68"/>
+      <c r="F50" s="68"/>
+      <c r="G50" s="68"/>
+      <c r="H50" s="68"/>
+      <c r="I50" s="68"/>
+      <c r="J50" s="68"/>
+      <c r="K50" s="68"/>
+      <c r="L50" s="68"/>
+      <c r="M50" s="68"/>
+      <c r="N50" s="68"/>
+      <c r="O50" s="68"/>
+      <c r="P50" s="68"/>
+      <c r="Q50" s="68"/>
+      <c r="R50" s="68"/>
+      <c r="S50" s="68"/>
+      <c r="T50" s="68"/>
+      <c r="U50" s="69"/>
+    </row>
+    <row r="51" spans="1:21" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="67"/>
+      <c r="B51" s="68"/>
+      <c r="C51" s="68"/>
+      <c r="D51" s="68"/>
+      <c r="E51" s="68"/>
+      <c r="F51" s="68"/>
+      <c r="G51" s="68"/>
+      <c r="H51" s="68"/>
+      <c r="I51" s="68"/>
+      <c r="J51" s="68"/>
+      <c r="K51" s="68"/>
+      <c r="L51" s="68"/>
+      <c r="M51" s="68"/>
+      <c r="N51" s="68"/>
+      <c r="O51" s="68"/>
+      <c r="P51" s="68"/>
+      <c r="Q51" s="68"/>
+      <c r="R51" s="68"/>
+      <c r="S51" s="68"/>
+      <c r="T51" s="68"/>
+      <c r="U51" s="69"/>
+    </row>
+    <row r="52" spans="1:21" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="67"/>
+      <c r="B52" s="68"/>
+      <c r="C52" s="68"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="68"/>
+      <c r="H52" s="68"/>
+      <c r="I52" s="68"/>
+      <c r="J52" s="68"/>
+      <c r="K52" s="68"/>
+      <c r="L52" s="68"/>
+      <c r="M52" s="68"/>
+      <c r="N52" s="68"/>
+      <c r="O52" s="68"/>
+      <c r="P52" s="68"/>
+      <c r="Q52" s="68"/>
+      <c r="R52" s="68"/>
+      <c r="S52" s="68"/>
+      <c r="T52" s="68"/>
+      <c r="U52" s="69"/>
+    </row>
+    <row r="53" spans="1:21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="67"/>
+      <c r="B53" s="68"/>
+      <c r="C53" s="68"/>
+      <c r="D53" s="68"/>
+      <c r="E53" s="68"/>
+      <c r="F53" s="68"/>
+      <c r="G53" s="68"/>
+      <c r="H53" s="68"/>
+      <c r="I53" s="68"/>
+      <c r="J53" s="68"/>
+      <c r="K53" s="68"/>
+      <c r="L53" s="68"/>
+      <c r="M53" s="68"/>
+      <c r="N53" s="68"/>
+      <c r="O53" s="68"/>
+      <c r="P53" s="68"/>
+      <c r="Q53" s="68"/>
+      <c r="R53" s="68"/>
+      <c r="S53" s="68"/>
+      <c r="T53" s="68"/>
+      <c r="U53" s="69"/>
+    </row>
+    <row r="54" spans="1:21" ht="12.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="31"/>
+      <c r="B54" s="32"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32"/>
+      <c r="F54" s="32"/>
+      <c r="G54" s="32"/>
+      <c r="H54" s="32"/>
+      <c r="I54" s="32"/>
+      <c r="J54" s="32"/>
+      <c r="K54" s="32"/>
+      <c r="L54" s="32"/>
+      <c r="M54" s="32"/>
+      <c r="N54" s="32"/>
+      <c r="O54" s="32"/>
+      <c r="P54" s="32"/>
+      <c r="Q54" s="32"/>
+      <c r="R54" s="32"/>
+      <c r="S54" s="32"/>
+      <c r="T54" s="32"/>
+      <c r="U54" s="33"/>
+    </row>
+    <row r="56" spans="1:21" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="57" spans="1:21" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="61" t="s">
         <v>225</v>
       </c>
-      <c r="B57" s="78"/>
-      <c r="C57" s="78"/>
-      <c r="D57" s="78"/>
-      <c r="E57" s="78"/>
-      <c r="F57" s="78"/>
-      <c r="G57" s="78"/>
-      <c r="H57" s="78"/>
-      <c r="I57" s="78"/>
-      <c r="J57" s="78"/>
-      <c r="K57" s="78"/>
-      <c r="L57" s="78"/>
-      <c r="M57" s="78"/>
-      <c r="N57" s="78"/>
-      <c r="O57" s="78"/>
-      <c r="P57" s="78"/>
-      <c r="Q57" s="78"/>
-      <c r="R57" s="78"/>
-      <c r="S57" s="78"/>
-      <c r="T57" s="78"/>
-      <c r="U57" s="79"/>
-    </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A58" s="80"/>
-      <c r="B58" s="81"/>
-      <c r="C58" s="81"/>
-      <c r="D58" s="81"/>
-      <c r="E58" s="81"/>
-      <c r="F58" s="81"/>
-      <c r="G58" s="81"/>
-      <c r="H58" s="81"/>
-      <c r="I58" s="81"/>
-      <c r="J58" s="81"/>
-      <c r="K58" s="81"/>
-      <c r="L58" s="81"/>
-      <c r="M58" s="81"/>
-      <c r="N58" s="81"/>
-      <c r="O58" s="81"/>
-      <c r="P58" s="81"/>
-      <c r="Q58" s="81"/>
-      <c r="R58" s="81"/>
-      <c r="S58" s="81"/>
-      <c r="T58" s="81"/>
-      <c r="U58" s="82"/>
-    </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A59" s="25" t="s">
+      <c r="B57" s="62"/>
+      <c r="C57" s="62"/>
+      <c r="D57" s="62"/>
+      <c r="E57" s="62"/>
+      <c r="F57" s="62"/>
+      <c r="G57" s="62"/>
+      <c r="H57" s="62"/>
+      <c r="I57" s="62"/>
+      <c r="J57" s="62"/>
+      <c r="K57" s="62"/>
+      <c r="L57" s="62"/>
+      <c r="M57" s="62"/>
+      <c r="N57" s="62"/>
+      <c r="O57" s="62"/>
+      <c r="P57" s="62"/>
+      <c r="Q57" s="62"/>
+      <c r="R57" s="62"/>
+      <c r="S57" s="62"/>
+      <c r="T57" s="62"/>
+      <c r="U57" s="63"/>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A58" s="64"/>
+      <c r="B58" s="65"/>
+      <c r="C58" s="65"/>
+      <c r="D58" s="65"/>
+      <c r="E58" s="65"/>
+      <c r="F58" s="65"/>
+      <c r="G58" s="65"/>
+      <c r="H58" s="65"/>
+      <c r="I58" s="65"/>
+      <c r="J58" s="65"/>
+      <c r="K58" s="65"/>
+      <c r="L58" s="65"/>
+      <c r="M58" s="65"/>
+      <c r="N58" s="65"/>
+      <c r="O58" s="65"/>
+      <c r="P58" s="65"/>
+      <c r="Q58" s="65"/>
+      <c r="R58" s="65"/>
+      <c r="S58" s="65"/>
+      <c r="T58" s="65"/>
+      <c r="U58" s="66"/>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A59" s="24" t="s">
         <v>128</v>
       </c>
-      <c r="B59" s="27"/>
-      <c r="C59" s="27" t="s">
+      <c r="B59" s="26"/>
+      <c r="C59" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
-      <c r="K59" s="27"/>
-      <c r="L59" s="27"/>
-      <c r="M59" s="27"/>
-      <c r="N59" s="27"/>
-      <c r="O59" s="27"/>
-      <c r="P59" s="27"/>
-      <c r="Q59" s="27"/>
-      <c r="R59" s="27"/>
-      <c r="S59" s="27"/>
-      <c r="T59" s="27"/>
-      <c r="U59" s="28"/>
-    </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A60" s="25"/>
-      <c r="B60" s="27"/>
-      <c r="C60" s="27"/>
-      <c r="D60" s="27"/>
-      <c r="E60" s="27"/>
-      <c r="F60" s="27"/>
-      <c r="G60" s="27"/>
-      <c r="H60" s="27"/>
-      <c r="I60" s="27"/>
-      <c r="J60" s="27"/>
-      <c r="K60" s="27"/>
-      <c r="L60" s="27"/>
-      <c r="M60" s="27"/>
-      <c r="N60" s="27"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="27"/>
-      <c r="Q60" s="27"/>
-      <c r="R60" s="27"/>
-      <c r="S60" s="27"/>
-      <c r="T60" s="27"/>
-      <c r="U60" s="28"/>
-    </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A61" s="71" t="s">
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="26"/>
+      <c r="I59" s="26"/>
+      <c r="J59" s="26"/>
+      <c r="K59" s="26"/>
+      <c r="L59" s="26"/>
+      <c r="M59" s="26"/>
+      <c r="N59" s="26"/>
+      <c r="O59" s="26"/>
+      <c r="P59" s="26"/>
+      <c r="Q59" s="26"/>
+      <c r="R59" s="26"/>
+      <c r="S59" s="26"/>
+      <c r="T59" s="26"/>
+      <c r="U59" s="27"/>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A60" s="24"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="26"/>
+      <c r="I60" s="26"/>
+      <c r="J60" s="26"/>
+      <c r="K60" s="26"/>
+      <c r="L60" s="26"/>
+      <c r="M60" s="26"/>
+      <c r="N60" s="26"/>
+      <c r="O60" s="26"/>
+      <c r="P60" s="26"/>
+      <c r="Q60" s="26"/>
+      <c r="R60" s="26"/>
+      <c r="S60" s="26"/>
+      <c r="T60" s="26"/>
+      <c r="U60" s="27"/>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A61" s="70" t="s">
         <v>226</v>
       </c>
-      <c r="B61" s="72"/>
-      <c r="C61" s="72"/>
-      <c r="D61" s="72"/>
-      <c r="E61" s="72"/>
-      <c r="F61" s="72"/>
-      <c r="G61" s="72"/>
-      <c r="H61" s="72"/>
-      <c r="I61" s="72"/>
-      <c r="J61" s="72"/>
-      <c r="K61" s="72"/>
-      <c r="L61" s="72"/>
-      <c r="M61" s="72"/>
-      <c r="N61" s="72"/>
-      <c r="O61" s="72"/>
-      <c r="P61" s="72"/>
-      <c r="Q61" s="72"/>
-      <c r="R61" s="72"/>
-      <c r="S61" s="72"/>
-      <c r="T61" s="72"/>
-      <c r="U61" s="73"/>
-    </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A62" s="71"/>
-      <c r="B62" s="72"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="72"/>
-      <c r="F62" s="72"/>
-      <c r="G62" s="72"/>
-      <c r="H62" s="72"/>
-      <c r="I62" s="72"/>
-      <c r="J62" s="72"/>
-      <c r="K62" s="72"/>
-      <c r="L62" s="72"/>
-      <c r="M62" s="72"/>
-      <c r="N62" s="72"/>
-      <c r="O62" s="72"/>
-      <c r="P62" s="72"/>
-      <c r="Q62" s="72"/>
-      <c r="R62" s="72"/>
-      <c r="S62" s="72"/>
-      <c r="T62" s="72"/>
-      <c r="U62" s="73"/>
-    </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A63" s="46" t="s">
+      <c r="B61" s="71"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="71"/>
+      <c r="J61" s="71"/>
+      <c r="K61" s="71"/>
+      <c r="L61" s="71"/>
+      <c r="M61" s="71"/>
+      <c r="N61" s="71"/>
+      <c r="O61" s="71"/>
+      <c r="P61" s="71"/>
+      <c r="Q61" s="71"/>
+      <c r="R61" s="71"/>
+      <c r="S61" s="71"/>
+      <c r="T61" s="71"/>
+      <c r="U61" s="72"/>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A62" s="70"/>
+      <c r="B62" s="71"/>
+      <c r="C62" s="71"/>
+      <c r="D62" s="71"/>
+      <c r="E62" s="71"/>
+      <c r="F62" s="71"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="71"/>
+      <c r="I62" s="71"/>
+      <c r="J62" s="71"/>
+      <c r="K62" s="71"/>
+      <c r="L62" s="71"/>
+      <c r="M62" s="71"/>
+      <c r="N62" s="71"/>
+      <c r="O62" s="71"/>
+      <c r="P62" s="71"/>
+      <c r="Q62" s="71"/>
+      <c r="R62" s="71"/>
+      <c r="S62" s="71"/>
+      <c r="T62" s="71"/>
+      <c r="U62" s="72"/>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A63" s="44" t="s">
         <v>227</v>
       </c>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="27"/>
-      <c r="K63" s="27"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
-      <c r="N63" s="27"/>
-      <c r="O63" s="27"/>
-      <c r="P63" s="27"/>
-      <c r="Q63" s="27"/>
-      <c r="R63" s="27"/>
-      <c r="S63" s="27"/>
-      <c r="T63" s="27"/>
-      <c r="U63" s="28"/>
-    </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A64" s="35" t="s">
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
+      <c r="D63" s="26"/>
+      <c r="E63" s="26"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="26"/>
+      <c r="I63" s="26"/>
+      <c r="J63" s="26"/>
+      <c r="K63" s="26"/>
+      <c r="L63" s="26"/>
+      <c r="M63" s="26"/>
+      <c r="N63" s="26"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="26"/>
+      <c r="Q63" s="26"/>
+      <c r="R63" s="26"/>
+      <c r="S63" s="26"/>
+      <c r="T63" s="26"/>
+      <c r="U63" s="27"/>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A64" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="B64" s="27"/>
-      <c r="C64" s="27"/>
-      <c r="D64" s="27"/>
-      <c r="E64" s="27"/>
-      <c r="F64" s="27"/>
-      <c r="G64" s="27"/>
-      <c r="H64" s="27"/>
-      <c r="I64" s="27"/>
-      <c r="J64" s="27"/>
-      <c r="K64" s="27"/>
-      <c r="L64" s="27"/>
-      <c r="M64" s="27"/>
-      <c r="N64" s="27"/>
-      <c r="O64" s="27"/>
-      <c r="P64" s="27"/>
-      <c r="Q64" s="27"/>
-      <c r="R64" s="27"/>
-      <c r="S64" s="27"/>
-      <c r="T64" s="27"/>
-      <c r="U64" s="28"/>
-    </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A65" s="30"/>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="H65" s="27"/>
-      <c r="I65" s="27"/>
-      <c r="J65" s="27"/>
-      <c r="K65" s="27"/>
-      <c r="L65" s="27"/>
-      <c r="M65" s="27"/>
-      <c r="N65" s="27"/>
-      <c r="O65" s="27"/>
-      <c r="P65" s="27"/>
-      <c r="Q65" s="27"/>
-      <c r="R65" s="27"/>
-      <c r="S65" s="27"/>
-      <c r="T65" s="27"/>
-      <c r="U65" s="28"/>
-    </row>
-    <row r="66" spans="1:21" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="35" t="s">
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="26"/>
+      <c r="I64" s="26"/>
+      <c r="J64" s="26"/>
+      <c r="K64" s="26"/>
+      <c r="L64" s="26"/>
+      <c r="M64" s="26"/>
+      <c r="N64" s="26"/>
+      <c r="O64" s="26"/>
+      <c r="P64" s="26"/>
+      <c r="Q64" s="26"/>
+      <c r="R64" s="26"/>
+      <c r="S64" s="26"/>
+      <c r="T64" s="26"/>
+      <c r="U64" s="27"/>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A65" s="29"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="26"/>
+      <c r="I65" s="26"/>
+      <c r="J65" s="26"/>
+      <c r="K65" s="26"/>
+      <c r="L65" s="26"/>
+      <c r="M65" s="26"/>
+      <c r="N65" s="26"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="26"/>
+      <c r="Q65" s="26"/>
+      <c r="R65" s="26"/>
+      <c r="S65" s="26"/>
+      <c r="T65" s="26"/>
+      <c r="U65" s="27"/>
+    </row>
+    <row r="66" spans="1:21" ht="14.5" x14ac:dyDescent="0.35">
+      <c r="A66" s="29" t="s">
         <v>219</v>
       </c>
-      <c r="B66" s="27"/>
-      <c r="C66" s="27"/>
-      <c r="D66" s="27"/>
-      <c r="E66" s="27"/>
-      <c r="F66" s="27"/>
-      <c r="G66" s="27"/>
-      <c r="H66" s="27"/>
-      <c r="I66" s="27"/>
-      <c r="J66" s="27"/>
-      <c r="K66" s="27"/>
-      <c r="L66" s="27"/>
-      <c r="M66" s="27"/>
-      <c r="N66" s="27"/>
-      <c r="O66" s="27"/>
-      <c r="P66" s="27"/>
-      <c r="Q66" s="27"/>
-      <c r="R66" s="27"/>
-      <c r="S66" s="27"/>
-      <c r="T66" s="27"/>
-      <c r="U66" s="28"/>
-    </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A67" s="71" t="s">
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="26"/>
+      <c r="I66" s="26"/>
+      <c r="J66" s="26"/>
+      <c r="K66" s="26"/>
+      <c r="L66" s="26"/>
+      <c r="M66" s="26"/>
+      <c r="N66" s="26"/>
+      <c r="O66" s="26"/>
+      <c r="P66" s="26"/>
+      <c r="Q66" s="26"/>
+      <c r="R66" s="26"/>
+      <c r="S66" s="26"/>
+      <c r="T66" s="26"/>
+      <c r="U66" s="27"/>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A67" s="70" t="s">
         <v>229</v>
       </c>
-      <c r="B67" s="72"/>
-      <c r="C67" s="72"/>
-      <c r="D67" s="72"/>
-      <c r="E67" s="72"/>
-      <c r="F67" s="72"/>
-      <c r="G67" s="72"/>
-      <c r="H67" s="72"/>
-      <c r="I67" s="72"/>
-      <c r="J67" s="72"/>
-      <c r="K67" s="72"/>
-      <c r="L67" s="72"/>
-      <c r="M67" s="72"/>
-      <c r="N67" s="72"/>
-      <c r="O67" s="72"/>
-      <c r="P67" s="72"/>
-      <c r="Q67" s="72"/>
-      <c r="R67" s="72"/>
-      <c r="S67" s="72"/>
-      <c r="T67" s="72"/>
-      <c r="U67" s="73"/>
-    </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A68" s="71"/>
-      <c r="B68" s="72"/>
-      <c r="C68" s="72"/>
-      <c r="D68" s="72"/>
-      <c r="E68" s="72"/>
-      <c r="F68" s="72"/>
-      <c r="G68" s="72"/>
-      <c r="H68" s="72"/>
-      <c r="I68" s="72"/>
-      <c r="J68" s="72"/>
-      <c r="K68" s="72"/>
-      <c r="L68" s="72"/>
-      <c r="M68" s="72"/>
-      <c r="N68" s="72"/>
-      <c r="O68" s="72"/>
-      <c r="P68" s="72"/>
-      <c r="Q68" s="72"/>
-      <c r="R68" s="72"/>
-      <c r="S68" s="72"/>
-      <c r="T68" s="72"/>
-      <c r="U68" s="73"/>
-    </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A69" s="46" t="s">
+      <c r="B67" s="71"/>
+      <c r="C67" s="71"/>
+      <c r="D67" s="71"/>
+      <c r="E67" s="71"/>
+      <c r="F67" s="71"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="71"/>
+      <c r="I67" s="71"/>
+      <c r="J67" s="71"/>
+      <c r="K67" s="71"/>
+      <c r="L67" s="71"/>
+      <c r="M67" s="71"/>
+      <c r="N67" s="71"/>
+      <c r="O67" s="71"/>
+      <c r="P67" s="71"/>
+      <c r="Q67" s="71"/>
+      <c r="R67" s="71"/>
+      <c r="S67" s="71"/>
+      <c r="T67" s="71"/>
+      <c r="U67" s="72"/>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A68" s="70"/>
+      <c r="B68" s="71"/>
+      <c r="C68" s="71"/>
+      <c r="D68" s="71"/>
+      <c r="E68" s="71"/>
+      <c r="F68" s="71"/>
+      <c r="G68" s="71"/>
+      <c r="H68" s="71"/>
+      <c r="I68" s="71"/>
+      <c r="J68" s="71"/>
+      <c r="K68" s="71"/>
+      <c r="L68" s="71"/>
+      <c r="M68" s="71"/>
+      <c r="N68" s="71"/>
+      <c r="O68" s="71"/>
+      <c r="P68" s="71"/>
+      <c r="Q68" s="71"/>
+      <c r="R68" s="71"/>
+      <c r="S68" s="71"/>
+      <c r="T68" s="71"/>
+      <c r="U68" s="72"/>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A69" s="44" t="s">
         <v>227</v>
       </c>
-      <c r="B69" s="27"/>
-      <c r="C69" s="27"/>
-      <c r="D69" s="27"/>
-      <c r="E69" s="27"/>
-      <c r="F69" s="27"/>
-      <c r="G69" s="27"/>
-      <c r="H69" s="27"/>
-      <c r="I69" s="27"/>
-      <c r="J69" s="27"/>
-      <c r="K69" s="27"/>
-      <c r="L69" s="27"/>
-      <c r="M69" s="27"/>
-      <c r="N69" s="27"/>
-      <c r="O69" s="27"/>
-      <c r="P69" s="27"/>
-      <c r="Q69" s="27"/>
-      <c r="R69" s="27"/>
-      <c r="S69" s="27"/>
-      <c r="T69" s="27"/>
-      <c r="U69" s="28"/>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A70" s="35" t="s">
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
+      <c r="D69" s="26"/>
+      <c r="E69" s="26"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="26"/>
+      <c r="I69" s="26"/>
+      <c r="J69" s="26"/>
+      <c r="K69" s="26"/>
+      <c r="L69" s="26"/>
+      <c r="M69" s="26"/>
+      <c r="N69" s="26"/>
+      <c r="O69" s="26"/>
+      <c r="P69" s="26"/>
+      <c r="Q69" s="26"/>
+      <c r="R69" s="26"/>
+      <c r="S69" s="26"/>
+      <c r="T69" s="26"/>
+      <c r="U69" s="27"/>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A70" s="29" t="s">
         <v>228</v>
       </c>
-      <c r="B70" s="27"/>
-      <c r="C70" s="27"/>
-      <c r="D70" s="27"/>
-      <c r="E70" s="27"/>
-      <c r="F70" s="27"/>
-      <c r="G70" s="27"/>
-      <c r="H70" s="27"/>
-      <c r="I70" s="27"/>
-      <c r="J70" s="27"/>
-      <c r="K70" s="27"/>
-      <c r="L70" s="27"/>
-      <c r="M70" s="27"/>
-      <c r="N70" s="27"/>
-      <c r="O70" s="27"/>
-      <c r="P70" s="27"/>
-      <c r="Q70" s="27"/>
-      <c r="R70" s="27"/>
-      <c r="S70" s="27"/>
-      <c r="T70" s="27"/>
-      <c r="U70" s="28"/>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A71" s="35"/>
-      <c r="B71" s="27"/>
-      <c r="C71" s="27"/>
-      <c r="D71" s="27"/>
-      <c r="E71" s="27"/>
-      <c r="F71" s="27"/>
-      <c r="G71" s="27"/>
-      <c r="H71" s="27"/>
-      <c r="I71" s="27"/>
-      <c r="J71" s="27"/>
-      <c r="K71" s="27"/>
-      <c r="L71" s="27"/>
-      <c r="M71" s="27"/>
-      <c r="N71" s="27"/>
-      <c r="O71" s="27"/>
-      <c r="P71" s="27"/>
-      <c r="Q71" s="27"/>
-      <c r="R71" s="27"/>
-      <c r="S71" s="27"/>
-      <c r="T71" s="27"/>
-      <c r="U71" s="28"/>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A72" s="30"/>
-      <c r="B72" s="27"/>
-      <c r="C72" s="27"/>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="27"/>
-      <c r="G72" s="27"/>
-      <c r="H72" s="27"/>
-      <c r="I72" s="27"/>
-      <c r="J72" s="27"/>
-      <c r="K72" s="27"/>
-      <c r="L72" s="27"/>
-      <c r="M72" s="27"/>
-      <c r="N72" s="27"/>
-      <c r="O72" s="27"/>
-      <c r="P72" s="27"/>
-      <c r="Q72" s="27"/>
-      <c r="R72" s="27"/>
-      <c r="S72" s="27"/>
-      <c r="T72" s="27"/>
-      <c r="U72" s="28"/>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A73" s="40" t="s">
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
+      <c r="D70" s="26"/>
+      <c r="E70" s="26"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="26"/>
+      <c r="I70" s="26"/>
+      <c r="J70" s="26"/>
+      <c r="K70" s="26"/>
+      <c r="L70" s="26"/>
+      <c r="M70" s="26"/>
+      <c r="N70" s="26"/>
+      <c r="O70" s="26"/>
+      <c r="P70" s="26"/>
+      <c r="Q70" s="26"/>
+      <c r="R70" s="26"/>
+      <c r="S70" s="26"/>
+      <c r="T70" s="26"/>
+      <c r="U70" s="27"/>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A71" s="29"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
+      <c r="D71" s="26"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="26"/>
+      <c r="I71" s="26"/>
+      <c r="J71" s="26"/>
+      <c r="K71" s="26"/>
+      <c r="L71" s="26"/>
+      <c r="M71" s="26"/>
+      <c r="N71" s="26"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="26"/>
+      <c r="Q71" s="26"/>
+      <c r="R71" s="26"/>
+      <c r="S71" s="26"/>
+      <c r="T71" s="26"/>
+      <c r="U71" s="27"/>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A72" s="29"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
+      <c r="D72" s="26"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
+      <c r="H72" s="26"/>
+      <c r="I72" s="26"/>
+      <c r="J72" s="26"/>
+      <c r="K72" s="26"/>
+      <c r="L72" s="26"/>
+      <c r="M72" s="26"/>
+      <c r="N72" s="26"/>
+      <c r="O72" s="26"/>
+      <c r="P72" s="26"/>
+      <c r="Q72" s="26"/>
+      <c r="R72" s="26"/>
+      <c r="S72" s="26"/>
+      <c r="T72" s="26"/>
+      <c r="U72" s="27"/>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A73" s="38" t="s">
         <v>180</v>
       </c>
-      <c r="B73" s="27"/>
-      <c r="C73" s="27"/>
-      <c r="D73" s="27"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="27"/>
-      <c r="G73" s="27"/>
-      <c r="H73" s="27"/>
-      <c r="I73" s="27"/>
-      <c r="J73" s="27"/>
-      <c r="K73" s="27"/>
-      <c r="L73" s="27"/>
-      <c r="M73" s="27"/>
-      <c r="N73" s="27"/>
-      <c r="O73" s="27"/>
-      <c r="P73" s="27"/>
-      <c r="Q73" s="27"/>
-      <c r="R73" s="27"/>
-      <c r="S73" s="27"/>
-      <c r="T73" s="27"/>
-      <c r="U73" s="28"/>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A74" s="30" t="s">
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
+      <c r="H73" s="26"/>
+      <c r="I73" s="26"/>
+      <c r="J73" s="26"/>
+      <c r="K73" s="26"/>
+      <c r="L73" s="26"/>
+      <c r="M73" s="26"/>
+      <c r="N73" s="26"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="26"/>
+      <c r="Q73" s="26"/>
+      <c r="R73" s="26"/>
+      <c r="S73" s="26"/>
+      <c r="T73" s="26"/>
+      <c r="U73" s="27"/>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A74" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="B74" s="27"/>
-      <c r="C74" s="27"/>
-      <c r="D74" s="27"/>
-      <c r="E74" s="27"/>
-      <c r="F74" s="27"/>
-      <c r="G74" s="27"/>
-      <c r="H74" s="27"/>
-      <c r="I74" s="27"/>
-      <c r="J74" s="27"/>
-      <c r="K74" s="27"/>
-      <c r="L74" s="27"/>
-      <c r="M74" s="27"/>
-      <c r="N74" s="27"/>
-      <c r="O74" s="27"/>
-      <c r="P74" s="27"/>
-      <c r="Q74" s="27"/>
-      <c r="R74" s="27"/>
-      <c r="S74" s="27"/>
-      <c r="T74" s="27"/>
-      <c r="U74" s="28"/>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A75" s="30" t="s">
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
+      <c r="H74" s="26"/>
+      <c r="I74" s="26"/>
+      <c r="J74" s="26"/>
+      <c r="K74" s="26"/>
+      <c r="L74" s="26"/>
+      <c r="M74" s="26"/>
+      <c r="N74" s="26"/>
+      <c r="O74" s="26"/>
+      <c r="P74" s="26"/>
+      <c r="Q74" s="26"/>
+      <c r="R74" s="26"/>
+      <c r="S74" s="26"/>
+      <c r="T74" s="26"/>
+      <c r="U74" s="27"/>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A75" s="29" t="s">
         <v>192</v>
       </c>
-      <c r="B75" s="27"/>
-      <c r="C75" s="27"/>
-      <c r="D75" s="27"/>
-      <c r="E75" s="27"/>
-      <c r="F75" s="27"/>
-      <c r="G75" s="27"/>
-      <c r="H75" s="27"/>
-      <c r="I75" s="27"/>
-      <c r="J75" s="27"/>
-      <c r="K75" s="27"/>
-      <c r="L75" s="27"/>
-      <c r="M75" s="27"/>
-      <c r="N75" s="27"/>
-      <c r="O75" s="27"/>
-      <c r="P75" s="27"/>
-      <c r="Q75" s="27"/>
-      <c r="R75" s="27"/>
-      <c r="S75" s="27"/>
-      <c r="T75" s="27"/>
-      <c r="U75" s="28"/>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A76" s="30" t="s">
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
+      <c r="H75" s="26"/>
+      <c r="I75" s="26"/>
+      <c r="J75" s="26"/>
+      <c r="K75" s="26"/>
+      <c r="L75" s="26"/>
+      <c r="M75" s="26"/>
+      <c r="N75" s="26"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="26"/>
+      <c r="Q75" s="26"/>
+      <c r="R75" s="26"/>
+      <c r="S75" s="26"/>
+      <c r="T75" s="26"/>
+      <c r="U75" s="27"/>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A76" s="29" t="s">
         <v>193</v>
       </c>
-      <c r="B76" s="27"/>
-      <c r="C76" s="27"/>
-      <c r="D76" s="27"/>
-      <c r="E76" s="27"/>
-      <c r="F76" s="27"/>
-      <c r="G76" s="27"/>
-      <c r="H76" s="27"/>
-      <c r="I76" s="27"/>
-      <c r="J76" s="27"/>
-      <c r="K76" s="27"/>
-      <c r="L76" s="27"/>
-      <c r="M76" s="27"/>
-      <c r="N76" s="27"/>
-      <c r="O76" s="27"/>
-      <c r="P76" s="27"/>
-      <c r="Q76" s="27"/>
-      <c r="R76" s="27"/>
-      <c r="S76" s="27"/>
-      <c r="T76" s="27"/>
-      <c r="U76" s="28"/>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A77" s="30" t="s">
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
+      <c r="H76" s="26"/>
+      <c r="I76" s="26"/>
+      <c r="J76" s="26"/>
+      <c r="K76" s="26"/>
+      <c r="L76" s="26"/>
+      <c r="M76" s="26"/>
+      <c r="N76" s="26"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="26"/>
+      <c r="Q76" s="26"/>
+      <c r="R76" s="26"/>
+      <c r="S76" s="26"/>
+      <c r="T76" s="26"/>
+      <c r="U76" s="27"/>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A77" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="B77" s="27"/>
-      <c r="C77" s="27"/>
-      <c r="D77" s="27"/>
-      <c r="E77" s="27"/>
-      <c r="F77" s="27"/>
-      <c r="G77" s="27"/>
-      <c r="H77" s="27"/>
-      <c r="I77" s="27"/>
-      <c r="J77" s="27"/>
-      <c r="K77" s="27"/>
-      <c r="L77" s="27"/>
-      <c r="M77" s="27"/>
-      <c r="N77" s="27"/>
-      <c r="O77" s="27"/>
-      <c r="P77" s="27"/>
-      <c r="Q77" s="27"/>
-      <c r="R77" s="27"/>
-      <c r="S77" s="27"/>
-      <c r="T77" s="27"/>
-      <c r="U77" s="28"/>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A78" s="30" t="s">
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
+      <c r="H77" s="26"/>
+      <c r="I77" s="26"/>
+      <c r="J77" s="26"/>
+      <c r="K77" s="26"/>
+      <c r="L77" s="26"/>
+      <c r="M77" s="26"/>
+      <c r="N77" s="26"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="26"/>
+      <c r="Q77" s="26"/>
+      <c r="R77" s="26"/>
+      <c r="S77" s="26"/>
+      <c r="T77" s="26"/>
+      <c r="U77" s="27"/>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A78" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="B78" s="27"/>
-      <c r="C78" s="27"/>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="27"/>
-      <c r="G78" s="27"/>
-      <c r="H78" s="27"/>
-      <c r="I78" s="27"/>
-      <c r="J78" s="27"/>
-      <c r="K78" s="27"/>
-      <c r="L78" s="27"/>
-      <c r="M78" s="27"/>
-      <c r="N78" s="27"/>
-      <c r="O78" s="27"/>
-      <c r="P78" s="27"/>
-      <c r="Q78" s="27"/>
-      <c r="R78" s="27"/>
-      <c r="S78" s="27"/>
-      <c r="T78" s="27"/>
-      <c r="U78" s="28"/>
-    </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A79" s="30" t="s">
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
+      <c r="H78" s="26"/>
+      <c r="I78" s="26"/>
+      <c r="J78" s="26"/>
+      <c r="K78" s="26"/>
+      <c r="L78" s="26"/>
+      <c r="M78" s="26"/>
+      <c r="N78" s="26"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="26"/>
+      <c r="Q78" s="26"/>
+      <c r="R78" s="26"/>
+      <c r="S78" s="26"/>
+      <c r="T78" s="26"/>
+      <c r="U78" s="27"/>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A79" s="29" t="s">
         <v>190</v>
       </c>
-      <c r="B79" s="27"/>
-      <c r="C79" s="27"/>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="27"/>
-      <c r="G79" s="27"/>
-      <c r="H79" s="27"/>
-      <c r="I79" s="27"/>
-      <c r="J79" s="27"/>
-      <c r="K79" s="27"/>
-      <c r="L79" s="27"/>
-      <c r="M79" s="27"/>
-      <c r="N79" s="27"/>
-      <c r="O79" s="27"/>
-      <c r="P79" s="27"/>
-      <c r="Q79" s="27"/>
-      <c r="R79" s="27"/>
-      <c r="S79" s="27"/>
-      <c r="T79" s="27"/>
-      <c r="U79" s="28"/>
-    </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A80" s="30"/>
-      <c r="B80" s="27"/>
-      <c r="C80" s="27"/>
-      <c r="D80" s="27"/>
-      <c r="E80" s="27"/>
-      <c r="F80" s="27"/>
-      <c r="G80" s="27"/>
-      <c r="H80" s="27"/>
-      <c r="I80" s="27"/>
-      <c r="J80" s="27"/>
-      <c r="K80" s="27"/>
-      <c r="L80" s="27"/>
-      <c r="M80" s="27"/>
-      <c r="N80" s="27"/>
-      <c r="O80" s="27"/>
-      <c r="P80" s="27"/>
-      <c r="Q80" s="27"/>
-      <c r="R80" s="27"/>
-      <c r="S80" s="27"/>
-      <c r="T80" s="27"/>
-      <c r="U80" s="28"/>
-    </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A81" s="30"/>
-      <c r="B81" s="27"/>
-      <c r="C81" s="27"/>
-      <c r="D81" s="27"/>
-      <c r="E81" s="27"/>
-      <c r="F81" s="27"/>
-      <c r="G81" s="27"/>
-      <c r="H81" s="27"/>
-      <c r="I81" s="27"/>
-      <c r="J81" s="27"/>
-      <c r="K81" s="27"/>
-      <c r="L81" s="27"/>
-      <c r="M81" s="27"/>
-      <c r="N81" s="27"/>
-      <c r="O81" s="27"/>
-      <c r="P81" s="27"/>
-      <c r="Q81" s="27"/>
-      <c r="R81" s="27"/>
-      <c r="S81" s="27"/>
-      <c r="T81" s="27"/>
-      <c r="U81" s="28"/>
-    </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A82" s="40" t="s">
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
+      <c r="D79" s="26"/>
+      <c r="E79" s="26"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
+      <c r="H79" s="26"/>
+      <c r="I79" s="26"/>
+      <c r="J79" s="26"/>
+      <c r="K79" s="26"/>
+      <c r="L79" s="26"/>
+      <c r="M79" s="26"/>
+      <c r="N79" s="26"/>
+      <c r="O79" s="26"/>
+      <c r="P79" s="26"/>
+      <c r="Q79" s="26"/>
+      <c r="R79" s="26"/>
+      <c r="S79" s="26"/>
+      <c r="T79" s="26"/>
+      <c r="U79" s="27"/>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A80" s="29"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
+      <c r="H80" s="26"/>
+      <c r="I80" s="26"/>
+      <c r="J80" s="26"/>
+      <c r="K80" s="26"/>
+      <c r="L80" s="26"/>
+      <c r="M80" s="26"/>
+      <c r="N80" s="26"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="26"/>
+      <c r="Q80" s="26"/>
+      <c r="R80" s="26"/>
+      <c r="S80" s="26"/>
+      <c r="T80" s="26"/>
+      <c r="U80" s="27"/>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A81" s="29"/>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
+      <c r="H81" s="26"/>
+      <c r="I81" s="26"/>
+      <c r="J81" s="26"/>
+      <c r="K81" s="26"/>
+      <c r="L81" s="26"/>
+      <c r="M81" s="26"/>
+      <c r="N81" s="26"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="26"/>
+      <c r="Q81" s="26"/>
+      <c r="R81" s="26"/>
+      <c r="S81" s="26"/>
+      <c r="T81" s="26"/>
+      <c r="U81" s="27"/>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A82" s="38" t="s">
         <v>181</v>
       </c>
-      <c r="B82" s="27"/>
-      <c r="C82" s="27"/>
-      <c r="D82" s="27"/>
-      <c r="E82" s="27"/>
-      <c r="F82" s="27"/>
-      <c r="G82" s="27"/>
-      <c r="H82" s="27"/>
-      <c r="I82" s="27"/>
-      <c r="J82" s="27"/>
-      <c r="K82" s="27"/>
-      <c r="L82" s="27"/>
-      <c r="M82" s="27"/>
-      <c r="N82" s="27"/>
-      <c r="O82" s="27"/>
-      <c r="P82" s="27"/>
-      <c r="Q82" s="27"/>
-      <c r="R82" s="27"/>
-      <c r="S82" s="27"/>
-      <c r="T82" s="27"/>
-      <c r="U82" s="28"/>
-    </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A83" s="42" t="s">
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
+      <c r="D82" s="26"/>
+      <c r="E82" s="26"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
+      <c r="H82" s="26"/>
+      <c r="I82" s="26"/>
+      <c r="J82" s="26"/>
+      <c r="K82" s="26"/>
+      <c r="L82" s="26"/>
+      <c r="M82" s="26"/>
+      <c r="N82" s="26"/>
+      <c r="O82" s="26"/>
+      <c r="P82" s="26"/>
+      <c r="Q82" s="26"/>
+      <c r="R82" s="26"/>
+      <c r="S82" s="26"/>
+      <c r="T82" s="26"/>
+      <c r="U82" s="27"/>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A83" s="40" t="s">
         <v>197</v>
       </c>
-      <c r="B83" s="27"/>
-      <c r="C83" s="27"/>
-      <c r="D83" s="27"/>
-      <c r="E83" s="27"/>
-      <c r="F83" s="27"/>
-      <c r="G83" s="27"/>
-      <c r="H83" s="27"/>
-      <c r="I83" s="27"/>
-      <c r="J83" s="27"/>
-      <c r="K83" s="27"/>
-      <c r="L83" s="27"/>
-      <c r="M83" s="27"/>
-      <c r="N83" s="27"/>
-      <c r="O83" s="27"/>
-      <c r="P83" s="27"/>
-      <c r="Q83" s="27"/>
-      <c r="R83" s="27"/>
-      <c r="S83" s="27"/>
-      <c r="T83" s="27"/>
-      <c r="U83" s="28"/>
-    </row>
-    <row r="84" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A84" s="42" t="s">
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
+      <c r="D83" s="26"/>
+      <c r="E83" s="26"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
+      <c r="H83" s="26"/>
+      <c r="I83" s="26"/>
+      <c r="J83" s="26"/>
+      <c r="K83" s="26"/>
+      <c r="L83" s="26"/>
+      <c r="M83" s="26"/>
+      <c r="N83" s="26"/>
+      <c r="O83" s="26"/>
+      <c r="P83" s="26"/>
+      <c r="Q83" s="26"/>
+      <c r="R83" s="26"/>
+      <c r="S83" s="26"/>
+      <c r="T83" s="26"/>
+      <c r="U83" s="27"/>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A84" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="B84" s="27"/>
-      <c r="C84" s="27"/>
-      <c r="D84" s="27"/>
-      <c r="E84" s="27"/>
-      <c r="F84" s="27"/>
-      <c r="G84" s="27"/>
-      <c r="H84" s="27"/>
-      <c r="I84" s="27"/>
-      <c r="J84" s="27"/>
-      <c r="K84" s="27"/>
-      <c r="L84" s="27"/>
-      <c r="M84" s="27"/>
-      <c r="N84" s="27"/>
-      <c r="O84" s="27"/>
-      <c r="P84" s="27"/>
-      <c r="Q84" s="27"/>
-      <c r="R84" s="27"/>
-      <c r="S84" s="27"/>
-      <c r="T84" s="27"/>
-      <c r="U84" s="28"/>
-    </row>
-    <row r="85" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A85" s="42" t="s">
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
+      <c r="D84" s="26"/>
+      <c r="E84" s="26"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
+      <c r="H84" s="26"/>
+      <c r="I84" s="26"/>
+      <c r="J84" s="26"/>
+      <c r="K84" s="26"/>
+      <c r="L84" s="26"/>
+      <c r="M84" s="26"/>
+      <c r="N84" s="26"/>
+      <c r="O84" s="26"/>
+      <c r="P84" s="26"/>
+      <c r="Q84" s="26"/>
+      <c r="R84" s="26"/>
+      <c r="S84" s="26"/>
+      <c r="T84" s="26"/>
+      <c r="U84" s="27"/>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A85" s="40" t="s">
         <v>196</v>
       </c>
-      <c r="B85" s="27"/>
-      <c r="C85" s="27"/>
-      <c r="D85" s="27"/>
-      <c r="E85" s="27"/>
-      <c r="F85" s="27"/>
-      <c r="G85" s="27"/>
-      <c r="H85" s="27"/>
-      <c r="I85" s="27"/>
-      <c r="J85" s="27"/>
-      <c r="K85" s="27"/>
-      <c r="L85" s="27"/>
-      <c r="M85" s="27"/>
-      <c r="N85" s="27"/>
-      <c r="O85" s="27"/>
-      <c r="P85" s="27"/>
-      <c r="Q85" s="27"/>
-      <c r="R85" s="27"/>
-      <c r="S85" s="27"/>
-      <c r="T85" s="27"/>
-      <c r="U85" s="28"/>
-    </row>
-    <row r="86" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A86" s="42" t="s">
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
+      <c r="D85" s="26"/>
+      <c r="E85" s="26"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
+      <c r="H85" s="26"/>
+      <c r="I85" s="26"/>
+      <c r="J85" s="26"/>
+      <c r="K85" s="26"/>
+      <c r="L85" s="26"/>
+      <c r="M85" s="26"/>
+      <c r="N85" s="26"/>
+      <c r="O85" s="26"/>
+      <c r="P85" s="26"/>
+      <c r="Q85" s="26"/>
+      <c r="R85" s="26"/>
+      <c r="S85" s="26"/>
+      <c r="T85" s="26"/>
+      <c r="U85" s="27"/>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A86" s="40" t="s">
         <v>190</v>
       </c>
-      <c r="B86" s="27"/>
-      <c r="C86" s="27"/>
-      <c r="D86" s="27"/>
-      <c r="E86" s="27"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="27"/>
-      <c r="H86" s="27"/>
-      <c r="I86" s="27"/>
-      <c r="J86" s="27"/>
-      <c r="K86" s="27"/>
-      <c r="L86" s="27"/>
-      <c r="M86" s="27"/>
-      <c r="N86" s="27"/>
-      <c r="O86" s="27"/>
-      <c r="P86" s="27"/>
-      <c r="Q86" s="27"/>
-      <c r="R86" s="27"/>
-      <c r="S86" s="27"/>
-      <c r="T86" s="27"/>
-      <c r="U86" s="28"/>
-    </row>
-    <row r="87" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A87" s="42" t="s">
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
+      <c r="D86" s="26"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
+      <c r="H86" s="26"/>
+      <c r="I86" s="26"/>
+      <c r="J86" s="26"/>
+      <c r="K86" s="26"/>
+      <c r="L86" s="26"/>
+      <c r="M86" s="26"/>
+      <c r="N86" s="26"/>
+      <c r="O86" s="26"/>
+      <c r="P86" s="26"/>
+      <c r="Q86" s="26"/>
+      <c r="R86" s="26"/>
+      <c r="S86" s="26"/>
+      <c r="T86" s="26"/>
+      <c r="U86" s="27"/>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A87" s="40" t="s">
         <v>198</v>
       </c>
-      <c r="B87" s="27"/>
-      <c r="C87" s="27"/>
-      <c r="D87" s="27"/>
-      <c r="E87" s="27"/>
-      <c r="F87" s="27"/>
-      <c r="G87" s="27"/>
-      <c r="H87" s="27"/>
-      <c r="I87" s="27"/>
-      <c r="J87" s="27"/>
-      <c r="K87" s="27"/>
-      <c r="L87" s="27"/>
-      <c r="M87" s="27"/>
-      <c r="N87" s="27"/>
-      <c r="O87" s="27"/>
-      <c r="P87" s="27"/>
-      <c r="Q87" s="27"/>
-      <c r="R87" s="27"/>
-      <c r="S87" s="27"/>
-      <c r="T87" s="27"/>
-      <c r="U87" s="28"/>
-    </row>
-    <row r="88" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A88" s="42"/>
-      <c r="B88" s="27"/>
-      <c r="C88" s="27"/>
-      <c r="D88" s="27"/>
-      <c r="E88" s="27"/>
-      <c r="F88" s="27"/>
-      <c r="G88" s="27"/>
-      <c r="H88" s="27"/>
-      <c r="I88" s="27"/>
-      <c r="J88" s="27"/>
-      <c r="K88" s="27"/>
-      <c r="L88" s="27"/>
-      <c r="M88" s="27"/>
-      <c r="N88" s="27"/>
-      <c r="O88" s="27"/>
-      <c r="P88" s="27"/>
-      <c r="Q88" s="27"/>
-      <c r="R88" s="27"/>
-      <c r="S88" s="27"/>
-      <c r="T88" s="27"/>
-      <c r="U88" s="28"/>
-    </row>
-    <row r="89" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A89" s="30"/>
-      <c r="B89" s="27"/>
-      <c r="C89" s="27"/>
-      <c r="D89" s="27"/>
-      <c r="E89" s="27"/>
-      <c r="F89" s="27"/>
-      <c r="G89" s="27"/>
-      <c r="H89" s="27"/>
-      <c r="I89" s="27"/>
-      <c r="J89" s="27"/>
-      <c r="K89" s="27"/>
-      <c r="L89" s="27"/>
-      <c r="M89" s="27"/>
-      <c r="N89" s="27"/>
-      <c r="O89" s="27"/>
-      <c r="P89" s="27"/>
-      <c r="Q89" s="27"/>
-      <c r="R89" s="27"/>
-      <c r="S89" s="27"/>
-      <c r="T89" s="27"/>
-      <c r="U89" s="28"/>
-    </row>
-    <row r="90" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A90" s="25" t="s">
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
+      <c r="D87" s="26"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="26"/>
+      <c r="G87" s="26"/>
+      <c r="H87" s="26"/>
+      <c r="I87" s="26"/>
+      <c r="J87" s="26"/>
+      <c r="K87" s="26"/>
+      <c r="L87" s="26"/>
+      <c r="M87" s="26"/>
+      <c r="N87" s="26"/>
+      <c r="O87" s="26"/>
+      <c r="P87" s="26"/>
+      <c r="Q87" s="26"/>
+      <c r="R87" s="26"/>
+      <c r="S87" s="26"/>
+      <c r="T87" s="26"/>
+      <c r="U87" s="27"/>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A88" s="40"/>
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
+      <c r="D88" s="26"/>
+      <c r="E88" s="26"/>
+      <c r="F88" s="26"/>
+      <c r="G88" s="26"/>
+      <c r="H88" s="26"/>
+      <c r="I88" s="26"/>
+      <c r="J88" s="26"/>
+      <c r="K88" s="26"/>
+      <c r="L88" s="26"/>
+      <c r="M88" s="26"/>
+      <c r="N88" s="26"/>
+      <c r="O88" s="26"/>
+      <c r="P88" s="26"/>
+      <c r="Q88" s="26"/>
+      <c r="R88" s="26"/>
+      <c r="S88" s="26"/>
+      <c r="T88" s="26"/>
+      <c r="U88" s="27"/>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A89" s="29"/>
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="26"/>
+      <c r="G89" s="26"/>
+      <c r="H89" s="26"/>
+      <c r="I89" s="26"/>
+      <c r="J89" s="26"/>
+      <c r="K89" s="26"/>
+      <c r="L89" s="26"/>
+      <c r="M89" s="26"/>
+      <c r="N89" s="26"/>
+      <c r="O89" s="26"/>
+      <c r="P89" s="26"/>
+      <c r="Q89" s="26"/>
+      <c r="R89" s="26"/>
+      <c r="S89" s="26"/>
+      <c r="T89" s="26"/>
+      <c r="U89" s="27"/>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A90" s="24" t="s">
         <v>224</v>
       </c>
-      <c r="B90" s="27"/>
-      <c r="C90" s="27"/>
-      <c r="D90" s="27"/>
-      <c r="E90" s="27"/>
-      <c r="F90" s="27"/>
-      <c r="G90" s="27"/>
-      <c r="H90" s="27"/>
-      <c r="I90" s="27"/>
-      <c r="J90" s="27"/>
-      <c r="K90" s="27"/>
-      <c r="L90" s="27"/>
-      <c r="M90" s="27"/>
-      <c r="N90" s="27"/>
-      <c r="O90" s="27"/>
-      <c r="P90" s="27"/>
-      <c r="Q90" s="27"/>
-      <c r="R90" s="27"/>
-      <c r="S90" s="27"/>
-      <c r="T90" s="27"/>
-      <c r="U90" s="28"/>
-    </row>
-    <row r="91" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A91" s="36" t="s">
+      <c r="B90" s="26"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="26"/>
+      <c r="E90" s="26"/>
+      <c r="F90" s="26"/>
+      <c r="G90" s="26"/>
+      <c r="H90" s="26"/>
+      <c r="I90" s="26"/>
+      <c r="J90" s="26"/>
+      <c r="K90" s="26"/>
+      <c r="L90" s="26"/>
+      <c r="M90" s="26"/>
+      <c r="N90" s="26"/>
+      <c r="O90" s="26"/>
+      <c r="P90" s="26"/>
+      <c r="Q90" s="26"/>
+      <c r="R90" s="26"/>
+      <c r="S90" s="26"/>
+      <c r="T90" s="26"/>
+      <c r="U90" s="27"/>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A91" s="34" t="s">
         <v>208</v>
       </c>
-      <c r="B91" s="27"/>
-      <c r="C91" s="27"/>
-      <c r="D91" s="27"/>
-      <c r="E91" s="27"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="27"/>
-      <c r="H91" s="27"/>
-      <c r="I91" s="27"/>
-      <c r="J91" s="27"/>
-      <c r="K91" s="27"/>
-      <c r="L91" s="27"/>
-      <c r="M91" s="27"/>
-      <c r="N91" s="27"/>
-      <c r="O91" s="27"/>
-      <c r="P91" s="27"/>
-      <c r="Q91" s="27"/>
-      <c r="R91" s="27"/>
-      <c r="S91" s="27"/>
-      <c r="T91" s="27"/>
-      <c r="U91" s="28"/>
-    </row>
-    <row r="92" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A92" s="36" t="s">
+      <c r="B91" s="26"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="26"/>
+      <c r="E91" s="26"/>
+      <c r="F91" s="26"/>
+      <c r="G91" s="26"/>
+      <c r="H91" s="26"/>
+      <c r="I91" s="26"/>
+      <c r="J91" s="26"/>
+      <c r="K91" s="26"/>
+      <c r="L91" s="26"/>
+      <c r="M91" s="26"/>
+      <c r="N91" s="26"/>
+      <c r="O91" s="26"/>
+      <c r="P91" s="26"/>
+      <c r="Q91" s="26"/>
+      <c r="R91" s="26"/>
+      <c r="S91" s="26"/>
+      <c r="T91" s="26"/>
+      <c r="U91" s="27"/>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A92" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="B92" s="27"/>
-      <c r="C92" s="27"/>
-      <c r="D92" s="27"/>
-      <c r="E92" s="27"/>
-      <c r="F92" s="27"/>
-      <c r="G92" s="27"/>
-      <c r="H92" s="27"/>
-      <c r="I92" s="27"/>
-      <c r="J92" s="27"/>
-      <c r="K92" s="27"/>
-      <c r="L92" s="27"/>
-      <c r="M92" s="27"/>
-      <c r="N92" s="27"/>
-      <c r="O92" s="27"/>
-      <c r="P92" s="27"/>
-      <c r="Q92" s="27"/>
-      <c r="R92" s="27"/>
-      <c r="S92" s="27"/>
-      <c r="T92" s="27"/>
-      <c r="U92" s="28"/>
-    </row>
-    <row r="93" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A93" s="74" t="s">
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="26"/>
+      <c r="F92" s="26"/>
+      <c r="G92" s="26"/>
+      <c r="H92" s="26"/>
+      <c r="I92" s="26"/>
+      <c r="J92" s="26"/>
+      <c r="K92" s="26"/>
+      <c r="L92" s="26"/>
+      <c r="M92" s="26"/>
+      <c r="N92" s="26"/>
+      <c r="O92" s="26"/>
+      <c r="P92" s="26"/>
+      <c r="Q92" s="26"/>
+      <c r="R92" s="26"/>
+      <c r="S92" s="26"/>
+      <c r="T92" s="26"/>
+      <c r="U92" s="27"/>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A93" s="67" t="s">
         <v>200</v>
       </c>
-      <c r="B93" s="75"/>
-      <c r="C93" s="75"/>
-      <c r="D93" s="75"/>
-      <c r="E93" s="75"/>
-      <c r="F93" s="75"/>
-      <c r="G93" s="75"/>
-      <c r="H93" s="75"/>
-      <c r="I93" s="75"/>
-      <c r="J93" s="75"/>
-      <c r="K93" s="75"/>
-      <c r="L93" s="75"/>
-      <c r="M93" s="75"/>
-      <c r="N93" s="75"/>
-      <c r="O93" s="75"/>
-      <c r="P93" s="75"/>
-      <c r="Q93" s="75"/>
-      <c r="R93" s="75"/>
-      <c r="S93" s="75"/>
-      <c r="T93" s="75"/>
-      <c r="U93" s="76"/>
-    </row>
-    <row r="94" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A94" s="74"/>
-      <c r="B94" s="75"/>
-      <c r="C94" s="75"/>
-      <c r="D94" s="75"/>
-      <c r="E94" s="75"/>
-      <c r="F94" s="75"/>
-      <c r="G94" s="75"/>
-      <c r="H94" s="75"/>
-      <c r="I94" s="75"/>
-      <c r="J94" s="75"/>
-      <c r="K94" s="75"/>
-      <c r="L94" s="75"/>
-      <c r="M94" s="75"/>
-      <c r="N94" s="75"/>
-      <c r="O94" s="75"/>
-      <c r="P94" s="75"/>
-      <c r="Q94" s="75"/>
-      <c r="R94" s="75"/>
-      <c r="S94" s="75"/>
-      <c r="T94" s="75"/>
-      <c r="U94" s="76"/>
-    </row>
-    <row r="95" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A95" s="74" t="s">
+      <c r="B93" s="68"/>
+      <c r="C93" s="68"/>
+      <c r="D93" s="68"/>
+      <c r="E93" s="68"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="68"/>
+      <c r="H93" s="68"/>
+      <c r="I93" s="68"/>
+      <c r="J93" s="68"/>
+      <c r="K93" s="68"/>
+      <c r="L93" s="68"/>
+      <c r="M93" s="68"/>
+      <c r="N93" s="68"/>
+      <c r="O93" s="68"/>
+      <c r="P93" s="68"/>
+      <c r="Q93" s="68"/>
+      <c r="R93" s="68"/>
+      <c r="S93" s="68"/>
+      <c r="T93" s="68"/>
+      <c r="U93" s="69"/>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A94" s="67"/>
+      <c r="B94" s="68"/>
+      <c r="C94" s="68"/>
+      <c r="D94" s="68"/>
+      <c r="E94" s="68"/>
+      <c r="F94" s="68"/>
+      <c r="G94" s="68"/>
+      <c r="H94" s="68"/>
+      <c r="I94" s="68"/>
+      <c r="J94" s="68"/>
+      <c r="K94" s="68"/>
+      <c r="L94" s="68"/>
+      <c r="M94" s="68"/>
+      <c r="N94" s="68"/>
+      <c r="O94" s="68"/>
+      <c r="P94" s="68"/>
+      <c r="Q94" s="68"/>
+      <c r="R94" s="68"/>
+      <c r="S94" s="68"/>
+      <c r="T94" s="68"/>
+      <c r="U94" s="69"/>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A95" s="67" t="s">
         <v>201</v>
       </c>
-      <c r="B95" s="75"/>
-      <c r="C95" s="75"/>
-      <c r="D95" s="75"/>
-      <c r="E95" s="75"/>
-      <c r="F95" s="75"/>
-      <c r="G95" s="75"/>
-      <c r="H95" s="75"/>
-      <c r="I95" s="75"/>
-      <c r="J95" s="75"/>
-      <c r="K95" s="75"/>
-      <c r="L95" s="75"/>
-      <c r="M95" s="75"/>
-      <c r="N95" s="75"/>
-      <c r="O95" s="75"/>
-      <c r="P95" s="75"/>
-      <c r="Q95" s="75"/>
-      <c r="R95" s="75"/>
-      <c r="S95" s="75"/>
-      <c r="T95" s="75"/>
-      <c r="U95" s="76"/>
-    </row>
-    <row r="96" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A96" s="74"/>
-      <c r="B96" s="75"/>
-      <c r="C96" s="75"/>
-      <c r="D96" s="75"/>
-      <c r="E96" s="75"/>
-      <c r="F96" s="75"/>
-      <c r="G96" s="75"/>
-      <c r="H96" s="75"/>
-      <c r="I96" s="75"/>
-      <c r="J96" s="75"/>
-      <c r="K96" s="75"/>
-      <c r="L96" s="75"/>
-      <c r="M96" s="75"/>
-      <c r="N96" s="75"/>
-      <c r="O96" s="75"/>
-      <c r="P96" s="75"/>
-      <c r="Q96" s="75"/>
-      <c r="R96" s="75"/>
-      <c r="S96" s="75"/>
-      <c r="T96" s="75"/>
-      <c r="U96" s="76"/>
-    </row>
-    <row r="97" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A97" s="36" t="s">
+      <c r="B95" s="68"/>
+      <c r="C95" s="68"/>
+      <c r="D95" s="68"/>
+      <c r="E95" s="68"/>
+      <c r="F95" s="68"/>
+      <c r="G95" s="68"/>
+      <c r="H95" s="68"/>
+      <c r="I95" s="68"/>
+      <c r="J95" s="68"/>
+      <c r="K95" s="68"/>
+      <c r="L95" s="68"/>
+      <c r="M95" s="68"/>
+      <c r="N95" s="68"/>
+      <c r="O95" s="68"/>
+      <c r="P95" s="68"/>
+      <c r="Q95" s="68"/>
+      <c r="R95" s="68"/>
+      <c r="S95" s="68"/>
+      <c r="T95" s="68"/>
+      <c r="U95" s="69"/>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A96" s="67"/>
+      <c r="B96" s="68"/>
+      <c r="C96" s="68"/>
+      <c r="D96" s="68"/>
+      <c r="E96" s="68"/>
+      <c r="F96" s="68"/>
+      <c r="G96" s="68"/>
+      <c r="H96" s="68"/>
+      <c r="I96" s="68"/>
+      <c r="J96" s="68"/>
+      <c r="K96" s="68"/>
+      <c r="L96" s="68"/>
+      <c r="M96" s="68"/>
+      <c r="N96" s="68"/>
+      <c r="O96" s="68"/>
+      <c r="P96" s="68"/>
+      <c r="Q96" s="68"/>
+      <c r="R96" s="68"/>
+      <c r="S96" s="68"/>
+      <c r="T96" s="68"/>
+      <c r="U96" s="69"/>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A97" s="34" t="s">
         <v>202</v>
       </c>
-      <c r="B97" s="27"/>
-      <c r="C97" s="27"/>
-      <c r="D97" s="27"/>
-      <c r="E97" s="27"/>
-      <c r="F97" s="27"/>
-      <c r="G97" s="27"/>
-      <c r="H97" s="27"/>
-      <c r="I97" s="27"/>
-      <c r="J97" s="27"/>
-      <c r="K97" s="27"/>
-      <c r="L97" s="27"/>
-      <c r="M97" s="27"/>
-      <c r="N97" s="27"/>
-      <c r="O97" s="27"/>
-      <c r="P97" s="27"/>
-      <c r="Q97" s="27"/>
-      <c r="R97" s="27"/>
-      <c r="S97" s="27"/>
-      <c r="T97" s="27"/>
-      <c r="U97" s="28"/>
-    </row>
-    <row r="98" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A98" s="74" t="s">
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26"/>
+      <c r="H97" s="26"/>
+      <c r="I97" s="26"/>
+      <c r="J97" s="26"/>
+      <c r="K97" s="26"/>
+      <c r="L97" s="26"/>
+      <c r="M97" s="26"/>
+      <c r="N97" s="26"/>
+      <c r="O97" s="26"/>
+      <c r="P97" s="26"/>
+      <c r="Q97" s="26"/>
+      <c r="R97" s="26"/>
+      <c r="S97" s="26"/>
+      <c r="T97" s="26"/>
+      <c r="U97" s="27"/>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A98" s="67" t="s">
         <v>203</v>
       </c>
-      <c r="B98" s="75"/>
-      <c r="C98" s="75"/>
-      <c r="D98" s="75"/>
-      <c r="E98" s="75"/>
-      <c r="F98" s="75"/>
-      <c r="G98" s="75"/>
-      <c r="H98" s="75"/>
-      <c r="I98" s="75"/>
-      <c r="J98" s="75"/>
-      <c r="K98" s="75"/>
-      <c r="L98" s="75"/>
-      <c r="M98" s="75"/>
-      <c r="N98" s="75"/>
-      <c r="O98" s="75"/>
-      <c r="P98" s="75"/>
-      <c r="Q98" s="75"/>
-      <c r="R98" s="75"/>
-      <c r="S98" s="75"/>
-      <c r="T98" s="75"/>
-      <c r="U98" s="76"/>
-    </row>
-    <row r="99" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A99" s="74"/>
-      <c r="B99" s="75"/>
-      <c r="C99" s="75"/>
-      <c r="D99" s="75"/>
-      <c r="E99" s="75"/>
-      <c r="F99" s="75"/>
-      <c r="G99" s="75"/>
-      <c r="H99" s="75"/>
-      <c r="I99" s="75"/>
-      <c r="J99" s="75"/>
-      <c r="K99" s="75"/>
-      <c r="L99" s="75"/>
-      <c r="M99" s="75"/>
-      <c r="N99" s="75"/>
-      <c r="O99" s="75"/>
-      <c r="P99" s="75"/>
-      <c r="Q99" s="75"/>
-      <c r="R99" s="75"/>
-      <c r="S99" s="75"/>
-      <c r="T99" s="75"/>
-      <c r="U99" s="76"/>
-    </row>
-    <row r="100" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A100" s="74" t="s">
+      <c r="B98" s="68"/>
+      <c r="C98" s="68"/>
+      <c r="D98" s="68"/>
+      <c r="E98" s="68"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="68"/>
+      <c r="H98" s="68"/>
+      <c r="I98" s="68"/>
+      <c r="J98" s="68"/>
+      <c r="K98" s="68"/>
+      <c r="L98" s="68"/>
+      <c r="M98" s="68"/>
+      <c r="N98" s="68"/>
+      <c r="O98" s="68"/>
+      <c r="P98" s="68"/>
+      <c r="Q98" s="68"/>
+      <c r="R98" s="68"/>
+      <c r="S98" s="68"/>
+      <c r="T98" s="68"/>
+      <c r="U98" s="69"/>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A99" s="67"/>
+      <c r="B99" s="68"/>
+      <c r="C99" s="68"/>
+      <c r="D99" s="68"/>
+      <c r="E99" s="68"/>
+      <c r="F99" s="68"/>
+      <c r="G99" s="68"/>
+      <c r="H99" s="68"/>
+      <c r="I99" s="68"/>
+      <c r="J99" s="68"/>
+      <c r="K99" s="68"/>
+      <c r="L99" s="68"/>
+      <c r="M99" s="68"/>
+      <c r="N99" s="68"/>
+      <c r="O99" s="68"/>
+      <c r="P99" s="68"/>
+      <c r="Q99" s="68"/>
+      <c r="R99" s="68"/>
+      <c r="S99" s="68"/>
+      <c r="T99" s="68"/>
+      <c r="U99" s="69"/>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A100" s="67" t="s">
         <v>204</v>
       </c>
-      <c r="B100" s="75"/>
-      <c r="C100" s="75"/>
-      <c r="D100" s="75"/>
-      <c r="E100" s="75"/>
-      <c r="F100" s="75"/>
-      <c r="G100" s="75"/>
-      <c r="H100" s="75"/>
-      <c r="I100" s="75"/>
-      <c r="J100" s="75"/>
-      <c r="K100" s="75"/>
-      <c r="L100" s="75"/>
-      <c r="M100" s="75"/>
-      <c r="N100" s="75"/>
-      <c r="O100" s="75"/>
-      <c r="P100" s="75"/>
-      <c r="Q100" s="75"/>
-      <c r="R100" s="75"/>
-      <c r="S100" s="75"/>
-      <c r="T100" s="75"/>
-      <c r="U100" s="76"/>
-    </row>
-    <row r="101" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A101" s="74"/>
-      <c r="B101" s="75"/>
-      <c r="C101" s="75"/>
-      <c r="D101" s="75"/>
-      <c r="E101" s="75"/>
-      <c r="F101" s="75"/>
-      <c r="G101" s="75"/>
-      <c r="H101" s="75"/>
-      <c r="I101" s="75"/>
-      <c r="J101" s="75"/>
-      <c r="K101" s="75"/>
-      <c r="L101" s="75"/>
-      <c r="M101" s="75"/>
-      <c r="N101" s="75"/>
-      <c r="O101" s="75"/>
-      <c r="P101" s="75"/>
-      <c r="Q101" s="75"/>
-      <c r="R101" s="75"/>
-      <c r="S101" s="75"/>
-      <c r="T101" s="75"/>
-      <c r="U101" s="76"/>
-    </row>
-    <row r="102" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A102" s="74"/>
-      <c r="B102" s="75"/>
-      <c r="C102" s="75"/>
-      <c r="D102" s="75"/>
-      <c r="E102" s="75"/>
-      <c r="F102" s="75"/>
-      <c r="G102" s="75"/>
-      <c r="H102" s="75"/>
-      <c r="I102" s="75"/>
-      <c r="J102" s="75"/>
-      <c r="K102" s="75"/>
-      <c r="L102" s="75"/>
-      <c r="M102" s="75"/>
-      <c r="N102" s="75"/>
-      <c r="O102" s="75"/>
-      <c r="P102" s="75"/>
-      <c r="Q102" s="75"/>
-      <c r="R102" s="75"/>
-      <c r="S102" s="75"/>
-      <c r="T102" s="75"/>
-      <c r="U102" s="76"/>
-    </row>
-    <row r="103" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A103" s="74"/>
-      <c r="B103" s="75"/>
-      <c r="C103" s="75"/>
-      <c r="D103" s="75"/>
-      <c r="E103" s="75"/>
-      <c r="F103" s="75"/>
-      <c r="G103" s="75"/>
-      <c r="H103" s="75"/>
-      <c r="I103" s="75"/>
-      <c r="J103" s="75"/>
-      <c r="K103" s="75"/>
-      <c r="L103" s="75"/>
-      <c r="M103" s="75"/>
-      <c r="N103" s="75"/>
-      <c r="O103" s="75"/>
-      <c r="P103" s="75"/>
-      <c r="Q103" s="75"/>
-      <c r="R103" s="75"/>
-      <c r="S103" s="75"/>
-      <c r="T103" s="75"/>
-      <c r="U103" s="76"/>
-    </row>
-    <row r="104" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A104" s="74" t="s">
+      <c r="B100" s="68"/>
+      <c r="C100" s="68"/>
+      <c r="D100" s="68"/>
+      <c r="E100" s="68"/>
+      <c r="F100" s="68"/>
+      <c r="G100" s="68"/>
+      <c r="H100" s="68"/>
+      <c r="I100" s="68"/>
+      <c r="J100" s="68"/>
+      <c r="K100" s="68"/>
+      <c r="L100" s="68"/>
+      <c r="M100" s="68"/>
+      <c r="N100" s="68"/>
+      <c r="O100" s="68"/>
+      <c r="P100" s="68"/>
+      <c r="Q100" s="68"/>
+      <c r="R100" s="68"/>
+      <c r="S100" s="68"/>
+      <c r="T100" s="68"/>
+      <c r="U100" s="69"/>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A101" s="67"/>
+      <c r="B101" s="68"/>
+      <c r="C101" s="68"/>
+      <c r="D101" s="68"/>
+      <c r="E101" s="68"/>
+      <c r="F101" s="68"/>
+      <c r="G101" s="68"/>
+      <c r="H101" s="68"/>
+      <c r="I101" s="68"/>
+      <c r="J101" s="68"/>
+      <c r="K101" s="68"/>
+      <c r="L101" s="68"/>
+      <c r="M101" s="68"/>
+      <c r="N101" s="68"/>
+      <c r="O101" s="68"/>
+      <c r="P101" s="68"/>
+      <c r="Q101" s="68"/>
+      <c r="R101" s="68"/>
+      <c r="S101" s="68"/>
+      <c r="T101" s="68"/>
+      <c r="U101" s="69"/>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A102" s="67"/>
+      <c r="B102" s="68"/>
+      <c r="C102" s="68"/>
+      <c r="D102" s="68"/>
+      <c r="E102" s="68"/>
+      <c r="F102" s="68"/>
+      <c r="G102" s="68"/>
+      <c r="H102" s="68"/>
+      <c r="I102" s="68"/>
+      <c r="J102" s="68"/>
+      <c r="K102" s="68"/>
+      <c r="L102" s="68"/>
+      <c r="M102" s="68"/>
+      <c r="N102" s="68"/>
+      <c r="O102" s="68"/>
+      <c r="P102" s="68"/>
+      <c r="Q102" s="68"/>
+      <c r="R102" s="68"/>
+      <c r="S102" s="68"/>
+      <c r="T102" s="68"/>
+      <c r="U102" s="69"/>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A103" s="67"/>
+      <c r="B103" s="68"/>
+      <c r="C103" s="68"/>
+      <c r="D103" s="68"/>
+      <c r="E103" s="68"/>
+      <c r="F103" s="68"/>
+      <c r="G103" s="68"/>
+      <c r="H103" s="68"/>
+      <c r="I103" s="68"/>
+      <c r="J103" s="68"/>
+      <c r="K103" s="68"/>
+      <c r="L103" s="68"/>
+      <c r="M103" s="68"/>
+      <c r="N103" s="68"/>
+      <c r="O103" s="68"/>
+      <c r="P103" s="68"/>
+      <c r="Q103" s="68"/>
+      <c r="R103" s="68"/>
+      <c r="S103" s="68"/>
+      <c r="T103" s="68"/>
+      <c r="U103" s="69"/>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A104" s="67" t="s">
         <v>205</v>
       </c>
-      <c r="B104" s="75"/>
-      <c r="C104" s="75"/>
-      <c r="D104" s="75"/>
-      <c r="E104" s="75"/>
-      <c r="F104" s="75"/>
-      <c r="G104" s="75"/>
-      <c r="H104" s="75"/>
-      <c r="I104" s="75"/>
-      <c r="J104" s="75"/>
-      <c r="K104" s="75"/>
-      <c r="L104" s="75"/>
-      <c r="M104" s="75"/>
-      <c r="N104" s="75"/>
-      <c r="O104" s="75"/>
-      <c r="P104" s="75"/>
-      <c r="Q104" s="75"/>
-      <c r="R104" s="75"/>
-      <c r="S104" s="75"/>
-      <c r="T104" s="75"/>
-      <c r="U104" s="76"/>
-    </row>
-    <row r="105" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A105" s="74"/>
-      <c r="B105" s="75"/>
-      <c r="C105" s="75"/>
-      <c r="D105" s="75"/>
-      <c r="E105" s="75"/>
-      <c r="F105" s="75"/>
-      <c r="G105" s="75"/>
-      <c r="H105" s="75"/>
-      <c r="I105" s="75"/>
-      <c r="J105" s="75"/>
-      <c r="K105" s="75"/>
-      <c r="L105" s="75"/>
-      <c r="M105" s="75"/>
-      <c r="N105" s="75"/>
-      <c r="O105" s="75"/>
-      <c r="P105" s="75"/>
-      <c r="Q105" s="75"/>
-      <c r="R105" s="75"/>
-      <c r="S105" s="75"/>
-      <c r="T105" s="75"/>
-      <c r="U105" s="76"/>
-    </row>
-    <row r="106" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A106" s="43"/>
-      <c r="B106" s="44"/>
-      <c r="C106" s="44"/>
-      <c r="D106" s="44"/>
-      <c r="E106" s="44"/>
-      <c r="F106" s="44"/>
-      <c r="G106" s="44"/>
-      <c r="H106" s="44"/>
-      <c r="I106" s="44"/>
-      <c r="J106" s="44"/>
-      <c r="K106" s="44"/>
-      <c r="L106" s="44"/>
-      <c r="M106" s="44"/>
-      <c r="N106" s="44"/>
-      <c r="O106" s="44"/>
-      <c r="P106" s="44"/>
-      <c r="Q106" s="44"/>
-      <c r="R106" s="44"/>
-      <c r="S106" s="44"/>
-      <c r="T106" s="44"/>
-      <c r="U106" s="45"/>
-    </row>
-    <row r="107" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="74" t="s">
+      <c r="B104" s="68"/>
+      <c r="C104" s="68"/>
+      <c r="D104" s="68"/>
+      <c r="E104" s="68"/>
+      <c r="F104" s="68"/>
+      <c r="G104" s="68"/>
+      <c r="H104" s="68"/>
+      <c r="I104" s="68"/>
+      <c r="J104" s="68"/>
+      <c r="K104" s="68"/>
+      <c r="L104" s="68"/>
+      <c r="M104" s="68"/>
+      <c r="N104" s="68"/>
+      <c r="O104" s="68"/>
+      <c r="P104" s="68"/>
+      <c r="Q104" s="68"/>
+      <c r="R104" s="68"/>
+      <c r="S104" s="68"/>
+      <c r="T104" s="68"/>
+      <c r="U104" s="69"/>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A105" s="67"/>
+      <c r="B105" s="68"/>
+      <c r="C105" s="68"/>
+      <c r="D105" s="68"/>
+      <c r="E105" s="68"/>
+      <c r="F105" s="68"/>
+      <c r="G105" s="68"/>
+      <c r="H105" s="68"/>
+      <c r="I105" s="68"/>
+      <c r="J105" s="68"/>
+      <c r="K105" s="68"/>
+      <c r="L105" s="68"/>
+      <c r="M105" s="68"/>
+      <c r="N105" s="68"/>
+      <c r="O105" s="68"/>
+      <c r="P105" s="68"/>
+      <c r="Q105" s="68"/>
+      <c r="R105" s="68"/>
+      <c r="S105" s="68"/>
+      <c r="T105" s="68"/>
+      <c r="U105" s="69"/>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A106" s="41"/>
+      <c r="B106" s="42"/>
+      <c r="C106" s="42"/>
+      <c r="D106" s="42"/>
+      <c r="E106" s="42"/>
+      <c r="F106" s="42"/>
+      <c r="G106" s="42"/>
+      <c r="H106" s="42"/>
+      <c r="I106" s="42"/>
+      <c r="J106" s="42"/>
+      <c r="K106" s="42"/>
+      <c r="L106" s="42"/>
+      <c r="M106" s="42"/>
+      <c r="N106" s="42"/>
+      <c r="O106" s="42"/>
+      <c r="P106" s="42"/>
+      <c r="Q106" s="42"/>
+      <c r="R106" s="42"/>
+      <c r="S106" s="42"/>
+      <c r="T106" s="42"/>
+      <c r="U106" s="43"/>
+    </row>
+    <row r="107" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="67" t="s">
         <v>206</v>
       </c>
-      <c r="B107" s="75"/>
-      <c r="C107" s="75"/>
-      <c r="D107" s="75"/>
-      <c r="E107" s="75"/>
-      <c r="F107" s="75"/>
-      <c r="G107" s="75"/>
-      <c r="H107" s="75"/>
-      <c r="I107" s="75"/>
-      <c r="J107" s="75"/>
-      <c r="K107" s="75"/>
-      <c r="L107" s="75"/>
-      <c r="M107" s="75"/>
-      <c r="N107" s="75"/>
-      <c r="O107" s="75"/>
-      <c r="P107" s="75"/>
-      <c r="Q107" s="75"/>
-      <c r="R107" s="75"/>
-      <c r="S107" s="75"/>
-      <c r="T107" s="75"/>
-      <c r="U107" s="76"/>
-    </row>
-    <row r="108" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="74"/>
-      <c r="B108" s="75"/>
-      <c r="C108" s="75"/>
-      <c r="D108" s="75"/>
-      <c r="E108" s="75"/>
-      <c r="F108" s="75"/>
-      <c r="G108" s="75"/>
-      <c r="H108" s="75"/>
-      <c r="I108" s="75"/>
-      <c r="J108" s="75"/>
-      <c r="K108" s="75"/>
-      <c r="L108" s="75"/>
-      <c r="M108" s="75"/>
-      <c r="N108" s="75"/>
-      <c r="O108" s="75"/>
-      <c r="P108" s="75"/>
-      <c r="Q108" s="75"/>
-      <c r="R108" s="75"/>
-      <c r="S108" s="75"/>
-      <c r="T108" s="75"/>
-      <c r="U108" s="76"/>
-    </row>
-    <row r="109" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="48"/>
-      <c r="B109" s="49"/>
-      <c r="C109" s="49"/>
-      <c r="D109" s="49"/>
-      <c r="E109" s="49"/>
-      <c r="F109" s="49"/>
-      <c r="G109" s="49"/>
-      <c r="H109" s="49"/>
-      <c r="I109" s="49"/>
-      <c r="J109" s="49"/>
-      <c r="K109" s="49"/>
-      <c r="L109" s="49"/>
-      <c r="M109" s="49"/>
-      <c r="N109" s="49"/>
-      <c r="O109" s="49"/>
-      <c r="P109" s="49"/>
-      <c r="Q109" s="49"/>
-      <c r="R109" s="49"/>
-      <c r="S109" s="49"/>
-      <c r="T109" s="49"/>
-      <c r="U109" s="50"/>
-    </row>
-    <row r="110" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="71" t="s">
+      <c r="B107" s="68"/>
+      <c r="C107" s="68"/>
+      <c r="D107" s="68"/>
+      <c r="E107" s="68"/>
+      <c r="F107" s="68"/>
+      <c r="G107" s="68"/>
+      <c r="H107" s="68"/>
+      <c r="I107" s="68"/>
+      <c r="J107" s="68"/>
+      <c r="K107" s="68"/>
+      <c r="L107" s="68"/>
+      <c r="M107" s="68"/>
+      <c r="N107" s="68"/>
+      <c r="O107" s="68"/>
+      <c r="P107" s="68"/>
+      <c r="Q107" s="68"/>
+      <c r="R107" s="68"/>
+      <c r="S107" s="68"/>
+      <c r="T107" s="68"/>
+      <c r="U107" s="69"/>
+    </row>
+    <row r="108" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="67"/>
+      <c r="B108" s="68"/>
+      <c r="C108" s="68"/>
+      <c r="D108" s="68"/>
+      <c r="E108" s="68"/>
+      <c r="F108" s="68"/>
+      <c r="G108" s="68"/>
+      <c r="H108" s="68"/>
+      <c r="I108" s="68"/>
+      <c r="J108" s="68"/>
+      <c r="K108" s="68"/>
+      <c r="L108" s="68"/>
+      <c r="M108" s="68"/>
+      <c r="N108" s="68"/>
+      <c r="O108" s="68"/>
+      <c r="P108" s="68"/>
+      <c r="Q108" s="68"/>
+      <c r="R108" s="68"/>
+      <c r="S108" s="68"/>
+      <c r="T108" s="68"/>
+      <c r="U108" s="69"/>
+    </row>
+    <row r="109" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="41"/>
+      <c r="B109" s="42"/>
+      <c r="C109" s="42"/>
+      <c r="D109" s="42"/>
+      <c r="E109" s="42"/>
+      <c r="F109" s="42"/>
+      <c r="G109" s="42"/>
+      <c r="H109" s="42"/>
+      <c r="I109" s="42"/>
+      <c r="J109" s="42"/>
+      <c r="K109" s="42"/>
+      <c r="L109" s="42"/>
+      <c r="M109" s="42"/>
+      <c r="N109" s="42"/>
+      <c r="O109" s="42"/>
+      <c r="P109" s="42"/>
+      <c r="Q109" s="42"/>
+      <c r="R109" s="42"/>
+      <c r="S109" s="42"/>
+      <c r="T109" s="42"/>
+      <c r="U109" s="43"/>
+    </row>
+    <row r="110" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="70" t="s">
         <v>221</v>
       </c>
-      <c r="B110" s="72"/>
-      <c r="C110" s="72"/>
-      <c r="D110" s="72"/>
-      <c r="E110" s="72"/>
-      <c r="F110" s="72"/>
-      <c r="G110" s="72"/>
-      <c r="H110" s="72"/>
-      <c r="I110" s="72"/>
-      <c r="J110" s="72"/>
-      <c r="K110" s="72"/>
-      <c r="L110" s="72"/>
-      <c r="M110" s="72"/>
-      <c r="N110" s="72"/>
-      <c r="O110" s="72"/>
-      <c r="P110" s="72"/>
-      <c r="Q110" s="72"/>
-      <c r="R110" s="72"/>
-      <c r="S110" s="72"/>
-      <c r="T110" s="72"/>
-      <c r="U110" s="73"/>
-    </row>
-    <row r="111" spans="1:21" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="71"/>
-      <c r="B111" s="72"/>
-      <c r="C111" s="72"/>
-      <c r="D111" s="72"/>
-      <c r="E111" s="72"/>
-      <c r="F111" s="72"/>
-      <c r="G111" s="72"/>
-      <c r="H111" s="72"/>
-      <c r="I111" s="72"/>
-      <c r="J111" s="72"/>
-      <c r="K111" s="72"/>
-      <c r="L111" s="72"/>
-      <c r="M111" s="72"/>
-      <c r="N111" s="72"/>
-      <c r="O111" s="72"/>
-      <c r="P111" s="72"/>
-      <c r="Q111" s="72"/>
-      <c r="R111" s="72"/>
-      <c r="S111" s="72"/>
-      <c r="T111" s="72"/>
-      <c r="U111" s="73"/>
-    </row>
-    <row r="112" spans="1:21" ht="13.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="37"/>
-      <c r="B112" s="38"/>
-      <c r="C112" s="38"/>
-      <c r="D112" s="38"/>
-      <c r="E112" s="38"/>
-      <c r="F112" s="38"/>
-      <c r="G112" s="38"/>
-      <c r="H112" s="38"/>
-      <c r="I112" s="38"/>
-      <c r="J112" s="38"/>
-      <c r="K112" s="38"/>
-      <c r="L112" s="38"/>
-      <c r="M112" s="38"/>
-      <c r="N112" s="38"/>
-      <c r="O112" s="38"/>
-      <c r="P112" s="38"/>
-      <c r="Q112" s="38"/>
-      <c r="R112" s="38"/>
-      <c r="S112" s="38"/>
-      <c r="T112" s="38"/>
-      <c r="U112" s="39"/>
-    </row>
-    <row r="113" spans="1:21" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B110" s="71"/>
+      <c r="C110" s="71"/>
+      <c r="D110" s="71"/>
+      <c r="E110" s="71"/>
+      <c r="F110" s="71"/>
+      <c r="G110" s="71"/>
+      <c r="H110" s="71"/>
+      <c r="I110" s="71"/>
+      <c r="J110" s="71"/>
+      <c r="K110" s="71"/>
+      <c r="L110" s="71"/>
+      <c r="M110" s="71"/>
+      <c r="N110" s="71"/>
+      <c r="O110" s="71"/>
+      <c r="P110" s="71"/>
+      <c r="Q110" s="71"/>
+      <c r="R110" s="71"/>
+      <c r="S110" s="71"/>
+      <c r="T110" s="71"/>
+      <c r="U110" s="72"/>
+    </row>
+    <row r="111" spans="1:21" ht="14" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="70"/>
+      <c r="B111" s="71"/>
+      <c r="C111" s="71"/>
+      <c r="D111" s="71"/>
+      <c r="E111" s="71"/>
+      <c r="F111" s="71"/>
+      <c r="G111" s="71"/>
+      <c r="H111" s="71"/>
+      <c r="I111" s="71"/>
+      <c r="J111" s="71"/>
+      <c r="K111" s="71"/>
+      <c r="L111" s="71"/>
+      <c r="M111" s="71"/>
+      <c r="N111" s="71"/>
+      <c r="O111" s="71"/>
+      <c r="P111" s="71"/>
+      <c r="Q111" s="71"/>
+      <c r="R111" s="71"/>
+      <c r="S111" s="71"/>
+      <c r="T111" s="71"/>
+      <c r="U111" s="72"/>
+    </row>
+    <row r="112" spans="1:21" ht="14" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="35"/>
+      <c r="B112" s="36"/>
+      <c r="C112" s="36"/>
+      <c r="D112" s="36"/>
+      <c r="E112" s="36"/>
+      <c r="F112" s="36"/>
+      <c r="G112" s="36"/>
+      <c r="H112" s="36"/>
+      <c r="I112" s="36"/>
+      <c r="J112" s="36"/>
+      <c r="K112" s="36"/>
+      <c r="L112" s="36"/>
+      <c r="M112" s="36"/>
+      <c r="N112" s="36"/>
+      <c r="O112" s="36"/>
+      <c r="P112" s="36"/>
+      <c r="Q112" s="36"/>
+      <c r="R112" s="36"/>
+      <c r="S112" s="36"/>
+      <c r="T112" s="36"/>
+      <c r="U112" s="37"/>
+    </row>
+    <row r="113" spans="1:21" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="10"/>
       <c r="B113" s="10"/>
       <c r="C113" s="10"/>
@@ -14307,7 +14275,7 @@
       <c r="T113" s="10"/>
       <c r="U113" s="10"/>
     </row>
-    <row r="114" spans="1:21" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:21" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="10"/>
       <c r="C114" s="10"/>
       <c r="D114" s="10"/>
@@ -14329,7 +14297,7 @@
       <c r="T114" s="10"/>
       <c r="U114" s="10"/>
     </row>
-    <row r="115" spans="1:21" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:21" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="10"/>
       <c r="B115" s="10"/>
       <c r="C115" s="10"/>
@@ -14352,7 +14320,7 @@
       <c r="T115" s="10"/>
       <c r="U115" s="10"/>
     </row>
-    <row r="116" spans="1:21" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:21" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="10"/>
       <c r="B116" s="10"/>
       <c r="C116" s="10"/>
@@ -14375,7 +14343,7 @@
       <c r="T116" s="10"/>
       <c r="U116" s="10"/>
     </row>
-    <row r="117" spans="1:21" ht="12.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:21" ht="12.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="10"/>
       <c r="B117" s="10"/>
       <c r="C117" s="10"/>
@@ -14400,11 +14368,6 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A7:U8"/>
-    <mergeCell ref="A57:U58"/>
-    <mergeCell ref="A93:U94"/>
-    <mergeCell ref="A95:U96"/>
-    <mergeCell ref="A98:U99"/>
     <mergeCell ref="A110:U111"/>
     <mergeCell ref="A10:U12"/>
     <mergeCell ref="A107:U108"/>
@@ -14416,15 +14379,26 @@
     <mergeCell ref="A104:U105"/>
     <mergeCell ref="A61:U62"/>
     <mergeCell ref="A67:U68"/>
+    <mergeCell ref="A7:U8"/>
+    <mergeCell ref="A57:U58"/>
+    <mergeCell ref="A93:U94"/>
+    <mergeCell ref="A95:U96"/>
+    <mergeCell ref="A98:U99"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="A13" r:id="rId1" location="consulter-sommaire"/>
-    <hyperlink ref="A18" r:id="rId2"/>
-    <hyperlink ref="A21" r:id="rId3"/>
-    <hyperlink ref="T5" r:id="rId4"/>
+    <hyperlink ref="A13" r:id="rId1" location="consulter-sommaire" xr:uid="{00000000-0004-0000-0300-000000000000}"/>
+    <hyperlink ref="A18" r:id="rId2" xr:uid="{00000000-0004-0000-0300-000001000000}"/>
+    <hyperlink ref="A21" r:id="rId3" xr:uid="{00000000-0004-0000-0300-000002000000}"/>
+    <hyperlink ref="T5" r:id="rId4" xr:uid="{00000000-0004-0000-0300-000003000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
   <drawing r:id="rId6"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{034a106e-6316-442c-ad35-738afd673d2b}" enabled="1" method="Standard" siteId="{cddc1229-ac2a-4b97-b78a-0e5cacb5865c}" removed="0"/>
+</clbl:labelList>
 </file>